--- a/files/九龙-马头角-壹沐第1期.xlsx
+++ b/files/九龙-马头角-壹沐第1期.xlsx
@@ -772,7 +772,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H3" s="5" t="n">
@@ -834,7 +834,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H4" s="5" t="n">
@@ -896,7 +896,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -958,7 +958,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -2144,7 +2144,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2578,7 +2578,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2640,7 +2640,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2764,7 +2764,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -2888,7 +2888,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -2950,7 +2950,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -3012,7 +3012,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -3074,7 +3074,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -3136,7 +3136,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -3198,7 +3198,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -3260,7 +3260,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -3322,7 +3322,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -3384,7 +3384,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -3446,7 +3446,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -3570,7 +3570,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -3756,7 +3756,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -3818,7 +3818,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -3880,7 +3880,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -3942,7 +3942,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -4190,7 +4190,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
@@ -4252,7 +4252,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -4376,7 +4376,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -4438,7 +4438,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -4500,7 +4500,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -4562,7 +4562,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
@@ -4624,7 +4624,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
@@ -4748,7 +4748,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="H67" s="5" t="n">
@@ -4810,7 +4810,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
@@ -4872,7 +4872,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -4934,7 +4934,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="H70" s="5" t="n">
@@ -4996,7 +4996,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -5058,7 +5058,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -5120,7 +5120,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -5182,7 +5182,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
@@ -5430,7 +5430,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="H78" s="5" t="n">
@@ -5492,7 +5492,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
@@ -5554,7 +5554,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
@@ -5616,7 +5616,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
@@ -5802,7 +5802,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="H84" s="5" t="n">
@@ -5864,7 +5864,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="H85" s="5" t="n">
@@ -5926,7 +5926,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="H86" s="5" t="n">
@@ -5988,7 +5988,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="H87" s="5" t="n">
@@ -6050,7 +6050,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H88" s="5" t="n">
@@ -6112,7 +6112,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="H89" s="5" t="n">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="H90" s="5" t="n">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="H91" s="5" t="n">
@@ -6298,7 +6298,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="H92" s="5" t="n">
@@ -6360,7 +6360,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="H93" s="5" t="n">
@@ -6422,7 +6422,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="H94" s="5" t="n">
@@ -6484,7 +6484,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
@@ -6546,7 +6546,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="H96" s="5" t="n">
@@ -6608,7 +6608,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H97" s="5" t="n">
@@ -6670,7 +6670,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="H98" s="5" t="n">
@@ -6732,7 +6732,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="H99" s="5" t="n">
@@ -6794,7 +6794,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="H100" s="5" t="n">
@@ -6856,7 +6856,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="H101" s="5" t="n">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="H102" s="5" t="n">
@@ -6980,7 +6980,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="H103" s="5" t="n">
@@ -7042,7 +7042,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="H104" s="5" t="n">
@@ -7104,7 +7104,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H105" s="5" t="n">
@@ -7166,7 +7166,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="H106" s="5" t="n">
@@ -7228,7 +7228,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H107" s="5" t="n">
@@ -7290,7 +7290,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="H108" s="5" t="n">
@@ -7352,7 +7352,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="H109" s="5" t="n">
@@ -7414,7 +7414,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="H110" s="5" t="n">
@@ -7476,7 +7476,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="H111" s="5" t="n">
@@ -7538,7 +7538,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H112" s="5" t="n">
@@ -7600,7 +7600,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H113" s="5" t="n">
@@ -7662,7 +7662,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H114" s="5" t="n">
@@ -7724,7 +7724,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="H115" s="5" t="n">
@@ -7786,7 +7786,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="H116" s="5" t="n">
@@ -7848,7 +7848,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="H117" s="5" t="n">
@@ -7910,7 +7910,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H118" s="5" t="n">
@@ -7972,7 +7972,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="H119" s="5" t="n">
@@ -8034,7 +8034,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H120" s="5" t="n">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H121" s="5" t="n">
@@ -8158,7 +8158,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H122" s="5" t="n">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="H123" s="5" t="n">
@@ -8282,7 +8282,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="H124" s="5" t="n">
@@ -8344,7 +8344,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="H125" s="5" t="n">
@@ -8406,7 +8406,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="H126" s="5" t="n">
@@ -8468,7 +8468,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="H127" s="5" t="n">
@@ -8530,7 +8530,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="H128" s="5" t="n">
@@ -8592,7 +8592,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="H129" s="5" t="n">
@@ -8654,7 +8654,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="H130" s="5" t="n">
@@ -8716,7 +8716,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="H131" s="5" t="n">
@@ -8778,7 +8778,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="H132" s="5" t="n">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="H133" s="5" t="n">
@@ -8902,7 +8902,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="H134" s="5" t="n">
@@ -8964,7 +8964,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H135" s="5" t="n">
@@ -9026,7 +9026,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H136" s="5" t="n">
@@ -9088,7 +9088,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="H137" s="5" t="n">
@@ -9150,7 +9150,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H138" s="5" t="n">
@@ -9212,7 +9212,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="H139" s="5" t="n">
@@ -9274,7 +9274,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="H140" s="5" t="n">
@@ -9336,7 +9336,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="H141" s="5" t="n">
@@ -9398,7 +9398,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H142" s="5" t="n">
@@ -9460,7 +9460,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H143" s="5" t="n">
@@ -9522,7 +9522,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="H144" s="5" t="n">
@@ -9584,7 +9584,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="H145" s="5" t="n">
@@ -9646,7 +9646,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="H146" s="5" t="n">
@@ -9708,7 +9708,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H147" s="5" t="n">
@@ -9770,7 +9770,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="H148" s="5" t="n">
@@ -9832,7 +9832,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="H149" s="5" t="n">
@@ -9894,7 +9894,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H150" s="5" t="n">
@@ -9956,7 +9956,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="H151" s="5" t="n">
@@ -10018,7 +10018,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H152" s="5" t="n">
@@ -10080,7 +10080,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="H153" s="5" t="n">
@@ -10142,7 +10142,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="H154" s="5" t="n">
@@ -10204,7 +10204,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="H155" s="5" t="n">
@@ -10266,7 +10266,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="H156" s="5" t="n">
@@ -10328,7 +10328,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="H157" s="5" t="n">
@@ -10390,7 +10390,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="H158" s="5" t="n">
@@ -10452,7 +10452,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H159" s="5" t="n">
@@ -10514,7 +10514,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2025-09-14</t>
         </is>
       </c>
       <c r="H160" s="5" t="n">
@@ -10576,7 +10576,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="H161" s="5" t="n">
@@ -10638,7 +10638,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="H162" s="5" t="n">
@@ -10700,7 +10700,7 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H163" s="5" t="n">
@@ -10762,7 +10762,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="H164" s="5" t="n">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="H165" s="5" t="n">
@@ -10886,7 +10886,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="H166" s="5" t="n">
@@ -10948,7 +10948,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="H167" s="5" t="n">
@@ -11010,7 +11010,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="H168" s="5" t="n">
@@ -11072,7 +11072,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="H169" s="5" t="n">
@@ -11134,7 +11134,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H170" s="5" t="n">
@@ -11196,7 +11196,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="H171" s="5" t="n">
@@ -11258,7 +11258,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="H172" s="5" t="n">
@@ -11320,7 +11320,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H173" s="5" t="n">
@@ -11382,7 +11382,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H174" s="5" t="n">
@@ -11444,7 +11444,7 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="H175" s="5" t="n">
@@ -11506,7 +11506,7 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="H176" s="5" t="n">
@@ -11568,7 +11568,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="H177" s="5" t="n">
@@ -11630,7 +11630,7 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="H178" s="5" t="n">
@@ -11692,7 +11692,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="H179" s="5" t="n">
@@ -11754,7 +11754,7 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="H180" s="5" t="n">
@@ -11816,7 +11816,7 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="H181" s="5" t="n">
@@ -11878,7 +11878,7 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H182" s="5" t="n">
@@ -11940,7 +11940,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H183" s="5" t="n">
@@ -12002,7 +12002,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="H184" s="5" t="n">
@@ -12064,7 +12064,7 @@
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="H185" s="5" t="n">
@@ -12126,7 +12126,7 @@
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="H186" s="5" t="n">
@@ -12188,7 +12188,7 @@
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="H187" s="5" t="n">
@@ -12250,7 +12250,7 @@
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="H188" s="5" t="n">
@@ -12312,7 +12312,7 @@
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H189" s="5" t="n">
@@ -12374,7 +12374,7 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="H190" s="5" t="n">
@@ -12436,7 +12436,7 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="H191" s="5" t="n">
@@ -12498,7 +12498,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="H192" s="5" t="n">
@@ -12560,7 +12560,7 @@
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="H193" s="5" t="n">
@@ -12622,7 +12622,7 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="H194" s="5" t="n">
@@ -12684,7 +12684,7 @@
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="H195" s="5" t="n">
@@ -12746,7 +12746,7 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="H196" s="5" t="n">
@@ -12808,7 +12808,7 @@
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H197" s="5" t="n">
@@ -12870,7 +12870,7 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H198" s="5" t="n">
@@ -12932,7 +12932,7 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="H199" s="5" t="n">
@@ -12994,7 +12994,7 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="H200" s="5" t="n">
@@ -13056,7 +13056,7 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="H201" s="5" t="n">
@@ -13118,7 +13118,7 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="H202" s="5" t="n">
@@ -13180,7 +13180,7 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="H203" s="5" t="n">
@@ -13242,7 +13242,7 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="H204" s="5" t="n">
@@ -13304,7 +13304,7 @@
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="H205" s="5" t="n">
@@ -13366,7 +13366,7 @@
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="H206" s="5" t="n">
@@ -13428,7 +13428,7 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="H207" s="5" t="n">
@@ -13490,7 +13490,7 @@
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="H208" s="5" t="n">
@@ -13552,7 +13552,7 @@
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="H209" s="5" t="n">
@@ -13614,7 +13614,7 @@
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="H210" s="5" t="n">
@@ -13676,7 +13676,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="H211" s="5" t="n">
@@ -13738,7 +13738,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H212" s="5" t="n">
@@ -13800,7 +13800,7 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="H213" s="5" t="n">
@@ -13862,7 +13862,7 @@
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2025-09-14</t>
         </is>
       </c>
       <c r="H214" s="5" t="n">
@@ -13924,7 +13924,7 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H215" s="5" t="n">
@@ -13986,7 +13986,7 @@
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="H216" s="5" t="n">
@@ -14048,7 +14048,7 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="H217" s="5" t="n">
@@ -14110,7 +14110,7 @@
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="H218" s="5" t="n">
@@ -14172,7 +14172,7 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="H219" s="5" t="n">
@@ -14234,7 +14234,7 @@
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="H220" s="5" t="n">
@@ -14296,7 +14296,7 @@
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="H221" s="5" t="n">
@@ -14358,7 +14358,7 @@
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="H222" s="5" t="n">
@@ -14420,7 +14420,7 @@
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>2026-01-11</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="H223" s="5" t="n">
@@ -14482,7 +14482,7 @@
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="H224" s="5" t="n">
@@ -14544,7 +14544,7 @@
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="H225" s="5" t="n">
@@ -14606,7 +14606,7 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H226" s="5" t="n">
@@ -14668,7 +14668,7 @@
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="H227" s="5" t="n">
@@ -14730,7 +14730,7 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H228" s="5" t="n">
@@ -14792,7 +14792,7 @@
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="H229" s="5" t="n">
@@ -14854,7 +14854,7 @@
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="H230" s="5" t="n">
@@ -14916,7 +14916,7 @@
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="H231" s="5" t="n">
@@ -14978,7 +14978,7 @@
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="H232" s="5" t="n">
@@ -15040,7 +15040,7 @@
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H233" s="5" t="n">
@@ -15102,7 +15102,7 @@
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H234" s="5" t="n">
@@ -15164,7 +15164,7 @@
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="H235" s="5" t="n">
@@ -15226,7 +15226,7 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="H236" s="5" t="n">
@@ -15288,7 +15288,7 @@
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="H237" s="5" t="n">
@@ -15350,7 +15350,7 @@
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="H238" s="5" t="n">
@@ -15412,7 +15412,7 @@
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="H239" s="5" t="n">
@@ -15474,7 +15474,7 @@
       </c>
       <c r="G240" s="3" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="H240" s="5" t="n">
@@ -15536,7 +15536,7 @@
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="H241" s="5" t="n">
@@ -15598,7 +15598,7 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="H242" s="5" t="n">
@@ -15660,7 +15660,7 @@
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="H243" s="5" t="n">
@@ -15722,7 +15722,7 @@
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="H244" s="5" t="n">
@@ -15784,7 +15784,7 @@
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="H245" s="5" t="n">
@@ -15846,7 +15846,7 @@
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="H246" s="5" t="n">
@@ -15908,7 +15908,7 @@
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H247" s="5" t="n">
@@ -15970,7 +15970,7 @@
       </c>
       <c r="G248" s="3" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="H248" s="5" t="n">
@@ -16032,7 +16032,7 @@
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="H249" s="5" t="n">
@@ -16094,7 +16094,7 @@
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="H250" s="5" t="n">
@@ -16156,7 +16156,7 @@
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="H251" s="5" t="n">
@@ -16218,7 +16218,7 @@
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="H252" s="5" t="n">
@@ -16280,7 +16280,7 @@
       </c>
       <c r="G253" s="3" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="H253" s="5" t="n">
@@ -16342,7 +16342,7 @@
       </c>
       <c r="G254" s="3" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="H254" s="5" t="n">
@@ -16404,7 +16404,7 @@
       </c>
       <c r="G255" s="3" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="H255" s="5" t="n">
@@ -16466,7 +16466,7 @@
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="H256" s="5" t="n">
@@ -16528,7 +16528,7 @@
       </c>
       <c r="G257" s="3" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="H257" s="5" t="n">
@@ -16590,7 +16590,7 @@
       </c>
       <c r="G258" s="3" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="H258" s="5" t="n">
@@ -16652,7 +16652,7 @@
       </c>
       <c r="G259" s="3" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="H259" s="5" t="n">
@@ -16714,7 +16714,7 @@
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="H260" s="5" t="n">
@@ -16776,7 +16776,7 @@
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="H261" s="5" t="n">
@@ -16838,7 +16838,7 @@
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="H262" s="5" t="n">
@@ -16900,7 +16900,7 @@
       </c>
       <c r="G263" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="H263" s="5" t="n">
@@ -16962,7 +16962,7 @@
       </c>
       <c r="G264" s="3" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H264" s="5" t="n">
@@ -17024,7 +17024,7 @@
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="H265" s="5" t="n">
@@ -17086,7 +17086,7 @@
       </c>
       <c r="G266" s="3" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="H266" s="5" t="n">
@@ -17148,7 +17148,7 @@
       </c>
       <c r="G267" s="3" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="H267" s="5" t="n">
@@ -17210,7 +17210,7 @@
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="H268" s="5" t="n">
@@ -17272,7 +17272,7 @@
       </c>
       <c r="G269" s="3" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="H269" s="5" t="n">
@@ -17334,7 +17334,7 @@
       </c>
       <c r="G270" s="3" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="H270" s="5" t="n">
@@ -17396,7 +17396,7 @@
       </c>
       <c r="G271" s="3" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="H271" s="5" t="n">
@@ -17458,7 +17458,7 @@
       </c>
       <c r="G272" s="3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H272" s="5" t="n">
@@ -17520,7 +17520,7 @@
       </c>
       <c r="G273" s="3" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="H273" s="5" t="n">
@@ -17582,7 +17582,7 @@
       </c>
       <c r="G274" s="3" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="H274" s="5" t="n">
@@ -17644,7 +17644,7 @@
       </c>
       <c r="G275" s="3" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H275" s="5" t="n">
@@ -17706,7 +17706,7 @@
       </c>
       <c r="G276" s="3" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="H276" s="5" t="n">
@@ -17768,7 +17768,7 @@
       </c>
       <c r="G277" s="3" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="H277" s="5" t="n">
@@ -17830,7 +17830,7 @@
       </c>
       <c r="G278" s="3" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="H278" s="5" t="n">
@@ -17892,7 +17892,7 @@
       </c>
       <c r="G279" s="3" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H279" s="5" t="n">
@@ -17954,7 +17954,7 @@
       </c>
       <c r="G280" s="3" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="H280" s="5" t="n">
@@ -18016,7 +18016,7 @@
       </c>
       <c r="G281" s="3" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="H281" s="5" t="n">
@@ -18078,7 +18078,7 @@
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>2025-12-14</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="H282" s="5" t="n">
@@ -18140,7 +18140,7 @@
       </c>
       <c r="G283" s="3" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="H283" s="5" t="n">
@@ -18202,7 +18202,7 @@
       </c>
       <c r="G284" s="3" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="H284" s="5" t="n">
@@ -18264,7 +18264,7 @@
       </c>
       <c r="G285" s="3" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="H285" s="5" t="n">
@@ -18326,7 +18326,7 @@
       </c>
       <c r="G286" s="3" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="H286" s="5" t="n">
@@ -18388,7 +18388,7 @@
       </c>
       <c r="G287" s="3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="H287" s="5" t="n">
@@ -18450,7 +18450,7 @@
       </c>
       <c r="G288" s="3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="H288" s="5" t="n">
@@ -18512,7 +18512,7 @@
       </c>
       <c r="G289" s="3" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="H289" s="5" t="n">
@@ -18574,7 +18574,7 @@
       </c>
       <c r="G290" s="3" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H290" s="5" t="n">
@@ -18636,7 +18636,7 @@
       </c>
       <c r="G291" s="3" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="H291" s="5" t="n">
@@ -18698,7 +18698,7 @@
       </c>
       <c r="G292" s="3" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="H292" s="5" t="n">
@@ -18760,7 +18760,7 @@
       </c>
       <c r="G293" s="3" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="H293" s="5" t="n">
@@ -18822,7 +18822,7 @@
       </c>
       <c r="G294" s="3" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H294" s="5" t="n">
@@ -18884,7 +18884,7 @@
       </c>
       <c r="G295" s="3" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2025-09-14</t>
         </is>
       </c>
       <c r="H295" s="5" t="n">
@@ -18946,7 +18946,7 @@
       </c>
       <c r="G296" s="3" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="H296" s="5" t="n">
@@ -19008,7 +19008,7 @@
       </c>
       <c r="G297" s="3" t="inlineStr">
         <is>
-          <t>2025-12-14</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="H297" s="5" t="n">
@@ -19070,7 +19070,7 @@
       </c>
       <c r="G298" s="3" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="H298" s="5" t="n">
@@ -19132,7 +19132,7 @@
       </c>
       <c r="G299" s="3" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="H299" s="5" t="n">
@@ -19194,7 +19194,7 @@
       </c>
       <c r="G300" s="3" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="H300" s="5" t="n">
@@ -19256,7 +19256,7 @@
       </c>
       <c r="G301" s="3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H301" s="5" t="n">
@@ -19318,7 +19318,7 @@
       </c>
       <c r="G302" s="3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="H302" s="5" t="n">
@@ -19380,7 +19380,7 @@
       </c>
       <c r="G303" s="3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="H303" s="5" t="n">
@@ -19442,7 +19442,7 @@
       </c>
       <c r="G304" s="3" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="H304" s="5" t="n">
@@ -19504,7 +19504,7 @@
       </c>
       <c r="G305" s="3" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H305" s="5" t="n">
@@ -19566,7 +19566,7 @@
       </c>
       <c r="G306" s="3" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="H306" s="5" t="n">
@@ -19628,7 +19628,7 @@
       </c>
       <c r="G307" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="H307" s="5" t="n">
@@ -19690,7 +19690,7 @@
       </c>
       <c r="G308" s="3" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="H308" s="5" t="n">
@@ -19752,7 +19752,7 @@
       </c>
       <c r="G309" s="3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="H309" s="5" t="n">
@@ -19814,7 +19814,7 @@
       </c>
       <c r="G310" s="3" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="H310" s="5" t="n">
@@ -19876,7 +19876,7 @@
       </c>
       <c r="G311" s="3" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="H311" s="5" t="n">
@@ -19938,7 +19938,7 @@
       </c>
       <c r="G312" s="3" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="H312" s="5" t="n">
@@ -20000,7 +20000,7 @@
       </c>
       <c r="G313" s="3" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="H313" s="5" t="n">
@@ -20062,7 +20062,7 @@
       </c>
       <c r="G314" s="3" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="H314" s="5" t="n">
@@ -20124,7 +20124,7 @@
       </c>
       <c r="G315" s="3" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="H315" s="5" t="n">
@@ -20186,7 +20186,7 @@
       </c>
       <c r="G316" s="3" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H316" s="5" t="n">
@@ -20248,7 +20248,7 @@
       </c>
       <c r="G317" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H317" s="5" t="n">
@@ -20310,7 +20310,7 @@
       </c>
       <c r="G318" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H318" s="5" t="n">
@@ -20372,7 +20372,7 @@
       </c>
       <c r="G319" s="3" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="H319" s="5" t="n">
@@ -20434,7 +20434,7 @@
       </c>
       <c r="G320" s="3" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H320" s="5" t="n">
@@ -20496,7 +20496,7 @@
       </c>
       <c r="G321" s="3" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="H321" s="5" t="n">
@@ -20558,7 +20558,7 @@
       </c>
       <c r="G322" s="3" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="H322" s="5" t="n">
@@ -20620,7 +20620,7 @@
       </c>
       <c r="G323" s="3" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="H323" s="5" t="n">
@@ -20682,7 +20682,7 @@
       </c>
       <c r="G324" s="3" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H324" s="5" t="n">
@@ -20744,7 +20744,7 @@
       </c>
       <c r="G325" s="3" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="H325" s="5" t="n">
@@ -20806,7 +20806,7 @@
       </c>
       <c r="G326" s="3" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="H326" s="5" t="n">
@@ -20868,7 +20868,7 @@
       </c>
       <c r="G327" s="3" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="H327" s="5" t="n">
@@ -20930,7 +20930,7 @@
       </c>
       <c r="G328" s="3" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="H328" s="5" t="n">
@@ -20992,7 +20992,7 @@
       </c>
       <c r="G329" s="3" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="H329" s="5" t="n">
@@ -21054,7 +21054,7 @@
       </c>
       <c r="G330" s="3" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="H330" s="5" t="n">
@@ -21116,7 +21116,7 @@
       </c>
       <c r="G331" s="3" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="H331" s="5" t="n">
@@ -21178,7 +21178,7 @@
       </c>
       <c r="G332" s="3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="H332" s="5" t="n">
@@ -21240,7 +21240,7 @@
       </c>
       <c r="G333" s="3" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H333" s="5" t="n">
@@ -21302,7 +21302,7 @@
       </c>
       <c r="G334" s="3" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="H334" s="5" t="n">
@@ -21364,7 +21364,7 @@
       </c>
       <c r="G335" s="3" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H335" s="5" t="n">
@@ -21426,7 +21426,7 @@
       </c>
       <c r="G336" s="3" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="H336" s="5" t="n">
@@ -21488,7 +21488,7 @@
       </c>
       <c r="G337" s="3" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="H337" s="5" t="n">
@@ -21550,7 +21550,7 @@
       </c>
       <c r="G338" s="3" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="H338" s="5" t="n">
@@ -21612,7 +21612,7 @@
       </c>
       <c r="G339" s="3" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H339" s="5" t="n">
@@ -21674,7 +21674,7 @@
       </c>
       <c r="G340" s="3" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="H340" s="5" t="n">
@@ -21736,7 +21736,7 @@
       </c>
       <c r="G341" s="3" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="H341" s="5" t="n">
@@ -21798,7 +21798,7 @@
       </c>
       <c r="G342" s="3" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="H342" s="5" t="n">
@@ -21860,7 +21860,7 @@
       </c>
       <c r="G343" s="3" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="H343" s="5" t="n">
@@ -21922,7 +21922,7 @@
       </c>
       <c r="G344" s="3" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="H344" s="5" t="n">
@@ -21984,7 +21984,7 @@
       </c>
       <c r="G345" s="3" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-06</t>
         </is>
       </c>
       <c r="H345" s="5" t="n">
@@ -22046,7 +22046,7 @@
       </c>
       <c r="G346" s="3" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="H346" s="5" t="n">
@@ -22108,7 +22108,7 @@
       </c>
       <c r="G347" s="3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H347" s="5" t="n">
@@ -22170,7 +22170,7 @@
       </c>
       <c r="G348" s="3" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="H348" s="5" t="n">
@@ -22232,7 +22232,7 @@
       </c>
       <c r="G349" s="3" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="H349" s="5" t="n">
@@ -22294,7 +22294,7 @@
       </c>
       <c r="G350" s="3" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H350" s="5" t="n">
@@ -22356,7 +22356,7 @@
       </c>
       <c r="G351" s="3" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="H351" s="5" t="n">
@@ -22418,7 +22418,7 @@
       </c>
       <c r="G352" s="3" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="H352" s="5" t="n">
@@ -22480,7 +22480,7 @@
       </c>
       <c r="G353" s="3" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="H353" s="5" t="n">
@@ -22542,7 +22542,7 @@
       </c>
       <c r="G354" s="3" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="H354" s="5" t="n">
@@ -22604,7 +22604,7 @@
       </c>
       <c r="G355" s="3" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="H355" s="5" t="n">
@@ -22666,7 +22666,7 @@
       </c>
       <c r="G356" s="3" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="H356" s="5" t="n">
@@ -22728,7 +22728,7 @@
       </c>
       <c r="G357" s="3" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="H357" s="5" t="n">
@@ -22790,7 +22790,7 @@
       </c>
       <c r="G358" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="H358" s="5" t="n">
@@ -22852,7 +22852,7 @@
       </c>
       <c r="G359" s="3" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="H359" s="5" t="n">
@@ -22914,7 +22914,7 @@
       </c>
       <c r="G360" s="3" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="H360" s="5" t="n">
@@ -22976,7 +22976,7 @@
       </c>
       <c r="G361" s="3" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="H361" s="5" t="n">
@@ -23038,7 +23038,7 @@
       </c>
       <c r="G362" s="3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H362" s="5" t="n">
@@ -23100,7 +23100,7 @@
       </c>
       <c r="G363" s="3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="H363" s="5" t="n">
@@ -23162,7 +23162,7 @@
       </c>
       <c r="G364" s="3" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="H364" s="5" t="n">
@@ -23224,7 +23224,7 @@
       </c>
       <c r="G365" s="3" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="H365" s="5" t="n">
@@ -23286,7 +23286,7 @@
       </c>
       <c r="G366" s="3" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="H366" s="5" t="n">
@@ -23348,7 +23348,7 @@
       </c>
       <c r="G367" s="3" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="H367" s="5" t="n">
@@ -23410,7 +23410,7 @@
       </c>
       <c r="G368" s="3" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="H368" s="5" t="n">
@@ -23472,7 +23472,7 @@
       </c>
       <c r="G369" s="3" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H369" s="5" t="n">
@@ -23534,7 +23534,7 @@
       </c>
       <c r="G370" s="3" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="H370" s="5" t="n">
@@ -23596,7 +23596,7 @@
       </c>
       <c r="G371" s="3" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="H371" s="5" t="n">
@@ -23658,7 +23658,7 @@
       </c>
       <c r="G372" s="3" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="H372" s="5" t="n">
@@ -23720,7 +23720,7 @@
       </c>
       <c r="G373" s="3" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="H373" s="5" t="n">
@@ -23782,7 +23782,7 @@
       </c>
       <c r="G374" s="3" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="H374" s="5" t="n">
@@ -23844,7 +23844,7 @@
       </c>
       <c r="G375" s="3" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="H375" s="5" t="n">
@@ -23906,7 +23906,7 @@
       </c>
       <c r="G376" s="3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="H376" s="5" t="n">
@@ -23968,7 +23968,7 @@
       </c>
       <c r="G377" s="3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="H377" s="5" t="n">
@@ -24030,7 +24030,7 @@
       </c>
       <c r="G378" s="3" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H378" s="5" t="n">
@@ -24092,7 +24092,7 @@
       </c>
       <c r="G379" s="3" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="H379" s="5" t="n">
@@ -24154,7 +24154,7 @@
       </c>
       <c r="G380" s="3" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="H380" s="5" t="n">
@@ -24216,7 +24216,7 @@
       </c>
       <c r="G381" s="3" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="H381" s="5" t="n">
@@ -24278,7 +24278,7 @@
       </c>
       <c r="G382" s="3" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="H382" s="5" t="n">
@@ -24340,7 +24340,7 @@
       </c>
       <c r="G383" s="3" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="H383" s="5" t="n">
@@ -24402,7 +24402,7 @@
       </c>
       <c r="G384" s="3" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H384" s="5" t="n">
@@ -24464,7 +24464,7 @@
       </c>
       <c r="G385" s="3" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="H385" s="5" t="n">
@@ -24526,7 +24526,7 @@
       </c>
       <c r="G386" s="3" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="H386" s="5" t="n">
@@ -24588,7 +24588,7 @@
       </c>
       <c r="G387" s="3" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="H387" s="5" t="n">
@@ -24650,7 +24650,7 @@
       </c>
       <c r="G388" s="3" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="H388" s="5" t="n">
@@ -24712,7 +24712,7 @@
       </c>
       <c r="G389" s="3" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="H389" s="5" t="n">
@@ -24774,7 +24774,7 @@
       </c>
       <c r="G390" s="3" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="H390" s="5" t="n">
@@ -24836,7 +24836,7 @@
       </c>
       <c r="G391" s="3" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="H391" s="5" t="n">
@@ -24898,7 +24898,7 @@
       </c>
       <c r="G392" s="3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="H392" s="5" t="n">
@@ -24960,7 +24960,7 @@
       </c>
       <c r="G393" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="H393" s="5" t="n">
@@ -25022,7 +25022,7 @@
       </c>
       <c r="G394" s="3" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="H394" s="5" t="n">
@@ -25084,7 +25084,7 @@
       </c>
       <c r="G395" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H395" s="5" t="n">
@@ -25146,7 +25146,7 @@
       </c>
       <c r="G396" s="3" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="H396" s="5" t="n">
@@ -25208,7 +25208,7 @@
       </c>
       <c r="G397" s="3" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H397" s="5" t="n">
@@ -25270,7 +25270,7 @@
       </c>
       <c r="G398" s="3" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="H398" s="5" t="n">
@@ -25332,7 +25332,7 @@
       </c>
       <c r="G399" s="3" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="H399" s="5" t="n">
@@ -25394,7 +25394,7 @@
       </c>
       <c r="G400" s="3" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="H400" s="5" t="n">
@@ -25456,7 +25456,7 @@
       </c>
       <c r="G401" s="3" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="H401" s="5" t="n">
@@ -25518,7 +25518,7 @@
       </c>
       <c r="G402" s="3" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="H402" s="5" t="n">
@@ -25580,7 +25580,7 @@
       </c>
       <c r="G403" s="3" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="H403" s="5" t="n">
@@ -25819,7 +25819,7 @@
           <t>B | 348呎 (2房)
 $814万
 $23,388/呎
-(26年-05月-20日)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="D5" s="21" t="inlineStr">
@@ -25827,7 +25827,7 @@
           <t>C | 349呎 (2房)
 $818万
 $23,439/呎
-(26年-05月-21日)</t>
+(26年-05月-22日)</t>
         </is>
       </c>
       <c r="E5" s="21" t="inlineStr">
@@ -25835,7 +25835,7 @@
           <t>D | 350呎 (2房)
 $822万
 $23,490/呎
-(26年-05月-14日)</t>
+(26年-05月-15日)</t>
         </is>
       </c>
       <c r="F5" s="21" t="inlineStr">
@@ -25843,7 +25843,7 @@
           <t>E | 269呎 (1房)
 $632万
 $23,507/呎
-(26年-06月-29日)</t>
+(26年-06月-30日)</t>
         </is>
       </c>
       <c r="G5" s="21" t="inlineStr">
@@ -25851,7 +25851,7 @@
           <t>F | 269呎 (1房)
 $634万
 $23,552/呎
-(26年-06月-01日)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="H5" s="22" t="inlineStr">
@@ -25867,7 +25867,7 @@
           <t>H | 320呎 (2房)
 $712万
 $22,259/呎
-(26年-05月-12日)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="J5" s="21" t="inlineStr">
@@ -25875,7 +25875,7 @@
           <t>J | 269呎 (1房)
 $589万
 $21,894/呎
-(26年-05月-17日)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="K5" s="21" t="inlineStr">
@@ -25883,7 +25883,7 @@
           <t>K | 272呎 (1房)
 $596万
 $21,928/呎
-(26年-05月-27日)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="L5" s="21" t="inlineStr">
@@ -25891,7 +25891,7 @@
           <t>L | 272呎 (1房)
 $598万
 $22,000/呎
-(26年-05月-21日)</t>
+(26年-05月-22日)</t>
         </is>
       </c>
       <c r="M5" s="21" t="inlineStr">
@@ -25899,7 +25899,7 @@
           <t>M | 271呎 (1房)
 $593万
 $21,881/呎
-(26年-04月-21日)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="N5" s="23" t="inlineStr"/>
@@ -25917,7 +25917,7 @@
           <t>A | 465呎 (3房)
 $1003万
 $21,571/呎
-(26年-03月-26日)</t>
+(26年-03月-27日)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr">
@@ -25925,7 +25925,7 @@
           <t>B | 349呎 (2房)
 $825万
 $23,632/呎
-(26年-05月-10日)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
       <c r="D6" s="21" t="inlineStr">
@@ -25933,7 +25933,7 @@
           <t>C | 349呎 (2房)
 $785万
 $22,488/呎
-(26年-05月-26日)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="E6" s="21" t="inlineStr">
@@ -25941,7 +25941,7 @@
           <t>D | 349呎 (2房)
 $712万
 $20,409/呎
-(25年-11月-03日)</t>
+(25年-11月-04日)</t>
         </is>
       </c>
       <c r="F6" s="21" t="inlineStr">
@@ -25949,7 +25949,7 @@
           <t>E | 350呎 (2房)
 $744万
 $21,246/呎
-(26年-04月-16日)</t>
+(26年-04月-17日)</t>
         </is>
       </c>
       <c r="G6" s="21" t="inlineStr">
@@ -25957,7 +25957,7 @@
           <t>F | 269呎 (1房)
 $596万
 $22,162/呎
-(26年-05月-18日)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="H6" s="21" t="inlineStr">
@@ -25965,7 +25965,7 @@
           <t>G | 269呎 (1房)
 $588万
 $21,873/呎
-(26年-04月-15日)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
       <c r="I6" s="21" t="inlineStr">
@@ -25973,7 +25973,7 @@
           <t>H | 379呎 (2房)
 $865万
 $22,815/呎
-(26年-05月-20日)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="J6" s="21" t="inlineStr">
@@ -25981,7 +25981,7 @@
           <t>J | 320呎 (2房)
 $662万
 $20,672/呎
-(26年-03月-30日)</t>
+(26年-03月-31日)</t>
         </is>
       </c>
       <c r="K6" s="21" t="inlineStr">
@@ -25989,7 +25989,7 @@
           <t>K | 269呎 (1房)
 $547万
 $20,333/呎
-(26年-03月-13日)</t>
+(26年-03月-14日)</t>
         </is>
       </c>
       <c r="L6" s="21" t="inlineStr">
@@ -25997,7 +25997,7 @@
           <t>L | 272呎 (1房)
 $531万
 $19,516/呎
-(26年-02月-09日)</t>
+(26年-02月-10日)</t>
         </is>
       </c>
       <c r="M6" s="21" t="inlineStr">
@@ -26005,7 +26005,7 @@
           <t>M | 272呎 (1房)
 $561万
 $20,632/呎
-(26年-04月-21日)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="N6" s="21" t="inlineStr">
@@ -26013,7 +26013,7 @@
           <t>N | 272呎 (1房)
 $572万
 $21,044/呎
-(26年-05月-12日)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="O6" s="21" t="inlineStr">
@@ -26021,7 +26021,7 @@
           <t>P | 268呎 (1房)
 $566万
 $21,121/呎
-(26年-05月-12日)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="P6" s="21" t="inlineStr">
@@ -26029,7 +26029,7 @@
           <t>Q | 367呎 (2房)
 $807万
 $21,981/呎
-(26年-05月-20日)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
     </row>
@@ -26044,7 +26044,7 @@
           <t>A | 465呎 (3房)
 $924万
 $19,879/呎
-(25年-10月-01日)</t>
+(25年-10月-02日)</t>
         </is>
       </c>
       <c r="C7" s="21" t="inlineStr">
@@ -26052,7 +26052,7 @@
           <t>B | 349呎 (2房)
 $749万
 $21,457/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
       <c r="D7" s="21" t="inlineStr">
@@ -26060,7 +26060,7 @@
           <t>C | 349呎 (2房)
 $725万
 $20,776/呎
-(26年-04月-12日)</t>
+(26年-04月-13日)</t>
         </is>
       </c>
       <c r="E7" s="21" t="inlineStr">
@@ -26068,7 +26068,7 @@
           <t>D | 349呎 (2房)
 $697万
 $19,958/呎
-(26年-02月-23日)</t>
+(26年-02月-24日)</t>
         </is>
       </c>
       <c r="F7" s="21" t="inlineStr">
@@ -26076,7 +26076,7 @@
           <t>E | 350呎 (2房)
 $712万
 $20,332/呎
-(26年-03月-20日)</t>
+(26年-03月-21日)</t>
         </is>
       </c>
       <c r="G7" s="21" t="inlineStr">
@@ -26084,7 +26084,7 @@
           <t>F | 269呎 (1房)
 $571万
 $21,230/呎
-(26年-04月-21日)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="H7" s="21" t="inlineStr">
@@ -26092,7 +26092,7 @@
           <t>G | 269呎 (1房)
 $564万
 $20,956/呎
-(26年-03月-24日)</t>
+(26年-03月-25日)</t>
         </is>
       </c>
       <c r="I7" s="21" t="inlineStr">
@@ -26100,7 +26100,7 @@
           <t>H | 379呎 (2房)
 $808万
 $21,306/呎
-(26年-04月-12日)</t>
+(26年-04月-13日)</t>
         </is>
       </c>
       <c r="J7" s="21" t="inlineStr">
@@ -26108,7 +26108,7 @@
           <t>J | 320呎 (2房)
 $632万
 $19,746/呎
-(26年-02月-28日)</t>
+(26年-03月-01日)</t>
         </is>
       </c>
       <c r="K7" s="21" t="inlineStr">
@@ -26116,7 +26116,7 @@
           <t>K | 269呎 (1房)
 $550万
 $20,454/呎
-(26年-04月-01日)</t>
+(26年-04月-02日)</t>
         </is>
       </c>
       <c r="L7" s="21" t="inlineStr">
@@ -26124,7 +26124,7 @@
           <t>L | 272呎 (1房)
 $510万
 $18,748/呎
-(26年-01月-06日)</t>
+(26年-01月-07日)</t>
         </is>
       </c>
       <c r="M7" s="21" t="inlineStr">
@@ -26132,7 +26132,7 @@
           <t>M | 272呎 (1房)
 $536万
 $19,710/呎
-(26年-04月-16日)</t>
+(26年-04月-17日)</t>
         </is>
       </c>
       <c r="N7" s="21" t="inlineStr">
@@ -26140,7 +26140,7 @@
           <t>N | 272呎 (1房)
 $547万
 $20,102/呎
-(26年-04月-28日)</t>
+(26年-04月-29日)</t>
         </is>
       </c>
       <c r="O7" s="21" t="inlineStr">
@@ -26148,7 +26148,7 @@
           <t>P | 268呎 (1房)
 $541万
 $20,169/呎
-(26年-04月-28日)</t>
+(26年-04月-29日)</t>
         </is>
       </c>
       <c r="P7" s="21" t="inlineStr">
@@ -26156,7 +26156,7 @@
           <t>Q | 367呎 (2房)
 $779万
 $21,233/呎
-(26年-04月-28日)</t>
+(26年-04月-29日)</t>
         </is>
       </c>
     </row>
@@ -26171,7 +26171,7 @@
           <t>A | 465呎 (3房)
 $929万
 $19,989/呎
-(25年-10月-01日)</t>
+(25年-10月-02日)</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr">
@@ -26179,7 +26179,7 @@
           <t>B | 349呎 (2房)
 $745万
 $21,334/呎
-(26年-05月-03日)</t>
+(26年-05月-04日)</t>
         </is>
       </c>
       <c r="D8" s="21" t="inlineStr">
@@ -26187,7 +26187,7 @@
           <t>C | 349呎 (2房)
 $721万
 $20,658/呎
-(26年-04月-12日)</t>
+(26年-04月-13日)</t>
         </is>
       </c>
       <c r="E8" s="21" t="inlineStr">
@@ -26195,7 +26195,7 @@
           <t>D | 349呎 (2房)
 $693万
 $19,844/呎
-(26年-02月-12日)</t>
+(26年-02月-13日)</t>
         </is>
       </c>
       <c r="F8" s="21" t="inlineStr">
@@ -26203,7 +26203,7 @@
           <t>E | 350呎 (2房)
 $745万
 $21,298/呎
-(26年-03月-16日)</t>
+(26年-03月-17日)</t>
         </is>
       </c>
       <c r="G8" s="21" t="inlineStr">
@@ -26211,7 +26211,7 @@
           <t>F | 269呎 (1房)
 $598万
 $22,245/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
       <c r="H8" s="21" t="inlineStr">
@@ -26219,7 +26219,7 @@
           <t>G | 269呎 (1房)
 $552万
 $20,507/呎
-(26年-02月-25日)</t>
+(26年-02月-26日)</t>
         </is>
       </c>
       <c r="I8" s="21" t="inlineStr">
@@ -26227,7 +26227,7 @@
           <t>H | 379呎 (2房)
 $803万
 $21,184/呎
-(26年-04月-16日)</t>
+(26年-04月-17日)</t>
         </is>
       </c>
       <c r="J8" s="21" t="inlineStr">
@@ -26235,7 +26235,7 @@
           <t>J | 320呎 (2房)
 $630万
 $19,690/呎
-(26年-04月-08日)</t>
+(26年-04月-09日)</t>
         </is>
       </c>
       <c r="K8" s="21" t="inlineStr">
@@ -26243,7 +26243,7 @@
           <t>K | 269呎 (1房)
 $523万
 $19,460/呎
-(26年-03月-31日)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
       <c r="L8" s="21" t="inlineStr">
@@ -26251,7 +26251,7 @@
           <t>L | 272呎 (1房)
 $522万
 $19,199/呎
-(25年-11月-05日)</t>
+(25年-11月-06日)</t>
         </is>
       </c>
       <c r="M8" s="21" t="inlineStr">
@@ -26259,7 +26259,7 @@
           <t>M | 272呎 (1房)
 $563万
 $20,703/呎
-(26年-04月-16日)</t>
+(26年-04月-17日)</t>
         </is>
       </c>
       <c r="N8" s="21" t="inlineStr">
@@ -26267,7 +26267,7 @@
           <t>N | 272呎 (1房)
 $545万
 $20,044/呎
-(26年-04月-26日)</t>
+(26年-04月-27日)</t>
         </is>
       </c>
       <c r="O8" s="21" t="inlineStr">
@@ -26275,7 +26275,7 @@
           <t>P | 268呎 (1房)
 $539万
 $20,109/呎
-(26年-05月-12日)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="P8" s="21" t="inlineStr">
@@ -26283,7 +26283,7 @@
           <t>Q | 367呎 (2房)
 $769万
 $20,947/呎
-(26年-05月-10日)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
     </row>
@@ -26298,7 +26298,7 @@
           <t>A | 465呎 (3房)
 $940万
 $20,207/呎
-(25年-10月-02日)</t>
+(25年-10月-03日)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr">
@@ -26306,7 +26306,7 @@
           <t>B | 349呎 (2房)
 $740万
 $21,213/呎
-(26年-04月-26日)</t>
+(26年-04月-27日)</t>
         </is>
       </c>
       <c r="D9" s="21" t="inlineStr">
@@ -26314,7 +26314,7 @@
           <t>C | 349呎 (2房)
 $717万
 $20,540/呎
-(26年-04月-12日)</t>
+(26年-04月-13日)</t>
         </is>
       </c>
       <c r="E9" s="21" t="inlineStr">
@@ -26322,7 +26322,7 @@
           <t>D | 349呎 (2房)
 $689万
 $19,731/呎
-(26年-02月-26日)</t>
+(26年-02月-27日)</t>
         </is>
       </c>
       <c r="F9" s="21" t="inlineStr">
@@ -26330,7 +26330,7 @@
           <t>E | 350呎 (2房)
 $704万
 $20,102/呎
-(26年-03月-30日)</t>
+(26年-03月-31日)</t>
         </is>
       </c>
       <c r="G9" s="21" t="inlineStr">
@@ -26338,7 +26338,7 @@
           <t>F | 269呎 (1房)
 $565万
 $20,997/呎
-(26年-04月-15日)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
       <c r="H9" s="21" t="inlineStr">
@@ -26346,7 +26346,7 @@
           <t>G | 269呎 (1房)
 $540万
 $20,061/呎
-(25年-10月-19日)</t>
+(25年-10月-20日)</t>
         </is>
       </c>
       <c r="I9" s="21" t="inlineStr">
@@ -26354,7 +26354,7 @@
           <t>H | 379呎 (2房)
 $760万
 $20,061/呎
-(25年-10月-05日)</t>
+(25年-10月-06日)</t>
         </is>
       </c>
       <c r="J9" s="21" t="inlineStr">
@@ -26362,7 +26362,7 @@
           <t>J | 320呎 (2房)
 $628万
 $19,632/呎
-(26年-03月-08日)</t>
+(26年-03月-09日)</t>
         </is>
       </c>
       <c r="K9" s="21" t="inlineStr">
@@ -26370,7 +26370,7 @@
           <t>K | 269呎 (1房)
 $519万
 $19,301/呎
-(26年-04月-09日)</t>
+(26年-04月-10日)</t>
         </is>
       </c>
       <c r="L9" s="21" t="inlineStr">
@@ -26378,7 +26378,7 @@
           <t>L | 272呎 (1房)
 $493万
 $18,136/呎
-(25年-11月-05日)</t>
+(25年-11月-06日)</t>
         </is>
       </c>
       <c r="M9" s="21" t="inlineStr">
@@ -26386,7 +26386,7 @@
           <t>M | 272呎 (1房)
 $539万
 $19,807/呎
-(26年-04月-16日)</t>
+(26年-04月-17日)</t>
         </is>
       </c>
       <c r="N9" s="21" t="inlineStr">
@@ -26394,7 +26394,7 @@
           <t>N | 272呎 (1房)
 $573万
 $21,054/呎
-(26年-05月-06日)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="O9" s="21" t="inlineStr">
@@ -26402,7 +26402,7 @@
           <t>P | 268呎 (1房)
 $543万
 $20,265/呎
-(26年-04月-27日)</t>
+(26年-04月-28日)</t>
         </is>
       </c>
       <c r="P9" s="21" t="inlineStr">
@@ -26410,7 +26410,7 @@
           <t>Q | 367呎 (2房)
 $767万
 $20,886/呎
-(26年-05月-10日)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
     </row>
@@ -26425,7 +26425,7 @@
           <t>A | 465呎 (3房)
 $914万
 $19,657/呎
-(25年-10月-05日)</t>
+(25年-10月-06日)</t>
         </is>
       </c>
       <c r="C10" s="21" t="inlineStr">
@@ -26433,7 +26433,7 @@
           <t>B | 349呎 (2房)
 $740万
 $21,213/呎
-(26年-04月-21日)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="D10" s="21" t="inlineStr">
@@ -26441,7 +26441,7 @@
           <t>C | 349呎 (2房)
 $717万
 $20,540/呎
-(26年-04月-12日)</t>
+(26年-04月-13日)</t>
         </is>
       </c>
       <c r="E10" s="21" t="inlineStr">
@@ -26449,7 +26449,7 @@
           <t>D | 349呎 (2房)
 $711万
 $20,374/呎
-(25年-10月-07日)</t>
+(25年-10月-08日)</t>
         </is>
       </c>
       <c r="F10" s="21" t="inlineStr">
@@ -26457,7 +26457,7 @@
           <t>E | 350呎 (2房)
 $704万
 $20,102/呎
-(26年-03月-24日)</t>
+(26年-03月-25日)</t>
         </is>
       </c>
       <c r="G10" s="21" t="inlineStr">
@@ -26465,7 +26465,7 @@
           <t>F | 269呎 (1房)
 $565万
 $20,997/呎
-(26年-04月-19日)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
       <c r="H10" s="21" t="inlineStr">
@@ -26473,7 +26473,7 @@
           <t>G | 269呎 (1房)
 $558万
 $20,726/呎
-(26年-03月-23日)</t>
+(26年-03月-24日)</t>
         </is>
       </c>
       <c r="I10" s="21" t="inlineStr">
@@ -26481,7 +26481,7 @@
           <t>H | 379呎 (2房)
 $790万
 $20,841/呎
-(26年-03月-19日)</t>
+(26年-03月-20日)</t>
         </is>
       </c>
       <c r="J10" s="21" t="inlineStr">
@@ -26489,7 +26489,7 @@
           <t>J | 320呎 (2房)
 $628万
 $19,632/呎
-(26年-03月-29日)</t>
+(26年-03月-30日)</t>
         </is>
       </c>
       <c r="K10" s="21" t="inlineStr">
@@ -26497,7 +26497,7 @@
           <t>K | 269呎 (1房)
 $519万
 $19,301/呎
-(26年-04月-14日)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="L10" s="21" t="inlineStr">
@@ -26505,7 +26505,7 @@
           <t>L | 272呎 (1房)
 $493万
 $18,136/呎
-(25年-10月-05日)</t>
+(25年-10月-06日)</t>
         </is>
       </c>
       <c r="M10" s="21" t="inlineStr">
@@ -26513,7 +26513,7 @@
           <t>M | 272呎 (1房)
 $533万
 $19,597/呎
-(26年-04月-13日)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
       <c r="N10" s="21" t="inlineStr">
@@ -26521,7 +26521,7 @@
           <t>N | 272呎 (1房)
 $544万
 $19,985/呎
-(26年-04月-28日)</t>
+(26年-04月-29日)</t>
         </is>
       </c>
       <c r="O10" s="21" t="inlineStr">
@@ -26529,7 +26529,7 @@
           <t>P | 268呎 (1房)
 $540万
 $20,157/呎
-(26年-05月-06日)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="P10" s="21" t="inlineStr">
@@ -26537,7 +26537,7 @@
           <t>Q | 367呎 (2房)
 $808万
 $22,003/呎
-(26年-04月-27日)</t>
+(26年-04月-28日)</t>
         </is>
       </c>
     </row>
@@ -26552,7 +26552,7 @@
           <t>A | 465呎 (3房)
 $909万
 $19,544/呎
-(25年-10月-05日)</t>
+(25年-10月-06日)</t>
         </is>
       </c>
       <c r="C11" s="21" t="inlineStr">
@@ -26560,7 +26560,7 @@
           <t>B | 349呎 (2房)
 $732万
 $20,966/呎
-(26年-05月-03日)</t>
+(26年-05月-04日)</t>
         </is>
       </c>
       <c r="D11" s="21" t="inlineStr">
@@ -26568,7 +26568,7 @@
           <t>C | 349呎 (2房)
 $709万
 $20,305/呎
-(26年-04月-12日)</t>
+(26年-04月-13日)</t>
         </is>
       </c>
       <c r="E11" s="21" t="inlineStr">
@@ -26576,7 +26576,7 @@
           <t>D | 349呎 (2房)
 $703万
 $20,143/呎
-(25年-11月-13日)</t>
+(25年-11月-14日)</t>
         </is>
       </c>
       <c r="F11" s="21" t="inlineStr">
@@ -26584,7 +26584,7 @@
           <t>E | 350呎 (2房)
 $703万
 $20,085/呎
-(26年-03月-26日)</t>
+(26年-03月-27日)</t>
         </is>
       </c>
       <c r="G11" s="21" t="inlineStr">
@@ -26592,7 +26592,7 @@
           <t>F | 269呎 (1房)
 $588万
 $21,875/呎
-(26年-04月-19日)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
       <c r="H11" s="21" t="inlineStr">
@@ -26600,7 +26600,7 @@
           <t>G | 269呎 (1房)
 $551万
 $20,497/呎
-(26年-03月-10日)</t>
+(26年-03月-11日)</t>
         </is>
       </c>
       <c r="I11" s="21" t="inlineStr">
@@ -26608,7 +26608,7 @@
           <t>H | 379呎 (2房)
 $781万
 $20,602/呎
-(26年-04月-20日)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="J11" s="21" t="inlineStr">
@@ -26616,7 +26616,7 @@
           <t>J | 320呎 (2房)
 $624万
 $19,515/呎
-(26年-04月-01日)</t>
+(26年-04月-02日)</t>
         </is>
       </c>
       <c r="K11" s="21" t="inlineStr">
@@ -26624,7 +26624,7 @@
           <t>K | 269呎 (1房)
 $516万
 $19,187/呎
-(26年-03月-30日)</t>
+(26年-03月-31日)</t>
         </is>
       </c>
       <c r="L11" s="21" t="inlineStr">
@@ -26632,7 +26632,7 @@
           <t>L | 272呎 (1房)
 $529万
 $19,432/呎
-(26年-02月-19日)</t>
+(26年-02月-20日)</t>
         </is>
       </c>
       <c r="M11" s="21" t="inlineStr">
@@ -26640,7 +26640,7 @@
           <t>M | 272呎 (1房)
 $536万
 $19,689/呎
-(26年-04月-13日)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
       <c r="N11" s="21" t="inlineStr">
@@ -26648,7 +26648,7 @@
           <t>N | 272呎 (1房)
 $540万
 $19,869/呎
-(26年-05月-07日)</t>
+(26年-05月-08日)</t>
         </is>
       </c>
       <c r="O11" s="21" t="inlineStr">
@@ -26656,7 +26656,7 @@
           <t>P | 268呎 (1房)
 $534万
 $19,931/呎
-(26年-05月-10日)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
       <c r="P11" s="21" t="inlineStr">
@@ -26664,7 +26664,7 @@
           <t>Q | 367呎 (2房)
 $803万
 $21,874/呎
-(26年-05月-07日)</t>
+(26年-05月-08日)</t>
         </is>
       </c>
     </row>
@@ -26679,7 +26679,7 @@
           <t>A | 465呎 (3房)
 $899万
 $19,326/呎
-(25年-10月-07日)</t>
+(25年-10月-08日)</t>
         </is>
       </c>
       <c r="C12" s="21" t="inlineStr">
@@ -26687,7 +26687,7 @@
           <t>B | 349呎 (2房)
 $713万
 $20,439/呎
-(26年-04月-16日)</t>
+(26年-04月-17日)</t>
         </is>
       </c>
       <c r="D12" s="21" t="inlineStr">
@@ -26695,7 +26695,7 @@
           <t>C | 349呎 (2房)
 $715万
 $20,492/呎
-(26年-04月-14日)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="E12" s="21" t="inlineStr">
@@ -26703,7 +26703,7 @@
           <t>D | 349呎 (2房)
 $699万
 $20,026/呎
-(25年-10月-08日)</t>
+(25年-10月-09日)</t>
         </is>
       </c>
       <c r="F12" s="21" t="inlineStr">
@@ -26711,7 +26711,7 @@
           <t>E | 350呎 (2房)
 $688万
 $19,652/呎
-(26年-03月-02日)</t>
+(26年-03月-03日)</t>
         </is>
       </c>
       <c r="G12" s="21" t="inlineStr">
@@ -26719,7 +26719,7 @@
           <t>F | 269呎 (1房)
 $555万
 $20,650/呎
-(26年-04月-21日)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="H12" s="21" t="inlineStr">
@@ -26727,7 +26727,7 @@
           <t>G | 269呎 (1房)
 $548万
 $20,382/呎
-(26年-03月-31日)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
       <c r="I12" s="21" t="inlineStr">
@@ -26735,7 +26735,7 @@
           <t>H | 379呎 (2房)
 $804万
 $21,206/呎
-(26年-05月-05日)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
       <c r="J12" s="21" t="inlineStr">
@@ -26743,7 +26743,7 @@
           <t>J | 320呎 (2房)
 $626万
 $19,561/呎
-(26年-01月-08日)</t>
+(26年-01月-09日)</t>
         </is>
       </c>
       <c r="K12" s="21" t="inlineStr">
@@ -26751,7 +26751,7 @@
           <t>K | 269呎 (1房)
 $515万
 $19,128/呎
-(26年-04月-01日)</t>
+(26年-04月-02日)</t>
         </is>
       </c>
       <c r="L12" s="21" t="inlineStr">
@@ -26759,7 +26759,7 @@
           <t>L | 272呎 (1房)
 $511万
 $18,776/呎
-(26年-01月-06日)</t>
+(26年-01月-07日)</t>
         </is>
       </c>
       <c r="M12" s="21" t="inlineStr">
@@ -26767,7 +26767,7 @@
           <t>M | 272呎 (1房)
 $534万
 $19,629/呎
-(26年-04月-12日)</t>
+(26年-04月-13日)</t>
         </is>
       </c>
       <c r="N12" s="21" t="inlineStr">
@@ -26775,7 +26775,7 @@
           <t>N | 272呎 (1房)
 $568万
 $20,869/呎
-(26年-05月-12日)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="O12" s="21" t="inlineStr">
@@ -26783,7 +26783,7 @@
           <t>P | 268呎 (1房)
 $533万
 $19,872/呎
-(26年-05月-14日)</t>
+(26年-05月-15日)</t>
         </is>
       </c>
       <c r="P12" s="21" t="inlineStr">
@@ -26791,7 +26791,7 @@
           <t>Q | 367呎 (2房)
 $760万
 $20,702/呎
-(26年-04月-22日)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
     </row>
@@ -26806,7 +26806,7 @@
           <t>A | 465呎 (3房)
 $933万
 $20,069/呎
-(26年-03月-24日)</t>
+(26年-03月-25日)</t>
         </is>
       </c>
       <c r="C13" s="21" t="inlineStr">
@@ -26814,7 +26814,7 @@
           <t>B | 349呎 (2房)
 $709万
 $20,318/呎
-(26年-04月-19日)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
       <c r="D13" s="21" t="inlineStr">
@@ -26822,7 +26822,7 @@
           <t>C | 349呎 (2房)
 $711万
 $20,374/呎
-(26年-04月-19日)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
       <c r="E13" s="21" t="inlineStr">
@@ -26830,7 +26830,7 @@
           <t>D | 349呎 (2房)
 $658万
 $18,861/呎
-(25年-10月-09日)</t>
+(25年-10月-10日)</t>
         </is>
       </c>
       <c r="F13" s="21" t="inlineStr">
@@ -26838,7 +26838,7 @@
           <t>E | 350呎 (2房)
 $662万
 $18,908/呎
-(25年-10月-09日)</t>
+(25年-10月-10日)</t>
         </is>
       </c>
       <c r="G13" s="21" t="inlineStr">
@@ -26846,7 +26846,7 @@
           <t>F | 269呎 (1房)
 $552万
 $20,532/呎
-(26年-04月-19日)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
       <c r="H13" s="21" t="inlineStr">
@@ -26854,7 +26854,7 @@
           <t>G | 269呎 (1房)
 $551万
 $20,484/呎
-(26年-04月-01日)</t>
+(26年-04月-02日)</t>
         </is>
       </c>
       <c r="I13" s="21" t="inlineStr">
@@ -26862,7 +26862,7 @@
           <t>H | 379呎 (2房)
 $799万
 $21,083/呎
-(26年-05月-10日)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
       <c r="J13" s="21" t="inlineStr">
@@ -26870,7 +26870,7 @@
           <t>J | 320呎 (2房)
 $619万
 $19,343/呎
-(26年-03月-23日)</t>
+(26年-03月-24日)</t>
         </is>
       </c>
       <c r="K13" s="21" t="inlineStr">
@@ -26878,7 +26878,7 @@
           <t>K | 269呎 (1房)
 $511万
 $19,013/呎
-(26年-04月-01日)</t>
+(26年-04月-02日)</t>
         </is>
       </c>
       <c r="L13" s="21" t="inlineStr">
@@ -26886,7 +26886,7 @@
           <t>L | 272呎 (1房)
 $489万
 $17,967/呎
-(25年-11月-27日)</t>
+(25年-11月-28日)</t>
         </is>
       </c>
       <c r="M13" s="21" t="inlineStr">
@@ -26894,7 +26894,7 @@
           <t>M | 272呎 (1房)
 $525万
 $19,308/呎
-(26年-04月-19日)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
       <c r="N13" s="21" t="inlineStr">
@@ -26902,7 +26902,7 @@
           <t>N | 272呎 (1房)
 $536万
 $19,693/呎
-(26年-04月-20日)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="O13" s="21" t="inlineStr">
@@ -26910,7 +26910,7 @@
           <t>P | 268呎 (1房)
 $532万
 $19,856/呎
-(26年-05月-05日)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
       <c r="P13" s="21" t="inlineStr">
@@ -26918,7 +26918,7 @@
           <t>Q | 367呎 (2房)
 $758万
 $20,641/呎
-(26年-04月-21日)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
     </row>
@@ -26933,7 +26933,7 @@
           <t>A | 465呎 (3房)
 $933万
 $20,058/呎
-(26年-03月-30日)</t>
+(26年-03月-31日)</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr">
@@ -26941,7 +26941,7 @@
           <t>B | 349呎 (2房)
 $705万
 $20,200/呎
-(26年-04月-13日)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
       <c r="D14" s="21" t="inlineStr">
@@ -26949,7 +26949,7 @@
           <t>C | 349呎 (2房)
 $707万
 $20,254/呎
-(26年-04月-09日)</t>
+(26年-04月-10日)</t>
         </is>
       </c>
       <c r="E14" s="21" t="inlineStr">
@@ -26957,7 +26957,7 @@
           <t>D | 349呎 (2房)
 $654万
 $18,750/呎
-(25年-10月-02日)</t>
+(25年-10月-03日)</t>
         </is>
       </c>
       <c r="F14" s="21" t="inlineStr">
@@ -26965,7 +26965,7 @@
           <t>E | 350呎 (2房)
 $658万
 $18,800/呎
-(25年-10月-13日)</t>
+(25年-10月-14日)</t>
         </is>
       </c>
       <c r="G14" s="21" t="inlineStr">
@@ -26973,7 +26973,7 @@
           <t>F | 269呎 (1房)
 $549万
 $20,417/呎
-(26年-04月-19日)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
       <c r="H14" s="21" t="inlineStr">
@@ -26981,7 +26981,7 @@
           <t>G | 269呎 (1房)
 $542万
 $20,153/呎
-(26年-04月-07日)</t>
+(26年-04月-08日)</t>
         </is>
       </c>
       <c r="I14" s="21" t="inlineStr">
@@ -26989,7 +26989,7 @@
           <t>H | 379呎 (2房)
 $794万
 $20,960/呎
-(26年-05月-05日)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
       <c r="J14" s="21" t="inlineStr">
@@ -26997,7 +26997,7 @@
           <t>J | 320呎 (2房)
 $655万
 $20,460/呎
-(26年-03月-29日)</t>
+(26年-03月-30日)</t>
         </is>
       </c>
       <c r="K14" s="21" t="inlineStr">
@@ -27005,7 +27005,7 @@
           <t>K | 269呎 (1房)
 $508万
 $18,898/呎
-(26年-04月-01日)</t>
+(26年-04月-02日)</t>
         </is>
       </c>
       <c r="L14" s="21" t="inlineStr">
@@ -27013,7 +27013,7 @@
           <t>L | 272呎 (1房)
 $488万
 $17,959/呎
-(25年-11月-06日)</t>
+(25年-11月-07日)</t>
         </is>
       </c>
       <c r="M14" s="21" t="inlineStr">
@@ -27021,7 +27021,7 @@
           <t>M | 272呎 (1房)
 $528万
 $19,397/呎
-(26年-04月-16日)</t>
+(26年-04月-17日)</t>
         </is>
       </c>
       <c r="N14" s="21" t="inlineStr">
@@ -27029,7 +27029,7 @@
           <t>N | 272呎 (1房)
 $561万
 $20,619/呎
-(26年-04月-27日)</t>
+(26年-04月-28日)</t>
         </is>
       </c>
       <c r="O14" s="21" t="inlineStr">
@@ -27037,7 +27037,7 @@
           <t>P | 268呎 (1房)
 $526万
 $19,631/呎
-(26年-05月-05日)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
       <c r="P14" s="21" t="inlineStr">
@@ -27045,7 +27045,7 @@
           <t>Q | 367呎 (2房)
 $741万
 $20,180/呎
-(26年-04月-16日)</t>
+(26年-04月-17日)</t>
         </is>
       </c>
     </row>
@@ -27060,7 +27060,7 @@
           <t>A | 465呎 (3房)
 $883万
 $18,993/呎
-(25年-10月-27日)</t>
+(25年-10月-28日)</t>
         </is>
       </c>
       <c r="C15" s="21" t="inlineStr">
@@ -27068,7 +27068,7 @@
           <t>B | 349呎 (2房)
 $727万
 $20,837/呎
-(26年-04月-08日)</t>
+(26年-04月-09日)</t>
         </is>
       </c>
       <c r="D15" s="21" t="inlineStr">
@@ -27076,7 +27076,7 @@
           <t>C | 349呎 (2房)
 $700万
 $20,045/呎
-(26年-03月-24日)</t>
+(26年-03月-25日)</t>
         </is>
       </c>
       <c r="E15" s="21" t="inlineStr">
@@ -27084,7 +27084,7 @@
           <t>D | 349呎 (2房)
 $687万
 $19,675/呎
-(25年-10月-09日)</t>
+(25年-10月-10日)</t>
         </is>
       </c>
       <c r="F15" s="21" t="inlineStr">
@@ -27092,7 +27092,7 @@
           <t>E | 350呎 (2房)
 $654万
 $18,689/呎
-(25年-09月-13日)</t>
+(25年-09月-14日)</t>
         </is>
       </c>
       <c r="G15" s="21" t="inlineStr">
@@ -27100,7 +27100,7 @@
           <t>F | 269呎 (1房)
 $557万
 $20,702/呎
-(26年-05月-12日)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="H15" s="21" t="inlineStr">
@@ -27108,7 +27108,7 @@
           <t>G | 269呎 (1房)
 $539万
 $20,038/呎
-(26年-04月-13日)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
       <c r="I15" s="21" t="inlineStr">
@@ -27116,7 +27116,7 @@
           <t>H | 379呎 (2房)
 $790万
 $20,836/呎
-(26年-05月-04日)</t>
+(26年-05月-05日)</t>
         </is>
       </c>
       <c r="J15" s="21" t="inlineStr">
@@ -27124,7 +27124,7 @@
           <t>J | 320呎 (2房)
 $646万
 $20,192/呎
-(26年-03月-16日)</t>
+(26年-03月-17日)</t>
         </is>
       </c>
       <c r="K15" s="21" t="inlineStr">
@@ -27132,7 +27132,7 @@
           <t>K | 269呎 (1房)
 $507万
 $18,842/呎
-(26年-04月-01日)</t>
+(26年-04月-02日)</t>
         </is>
       </c>
       <c r="L15" s="21" t="inlineStr">
@@ -27140,7 +27140,7 @@
           <t>L | 272呎 (1房)
 $482万
 $17,709/呎
-(25年-11月-24日)</t>
+(25年-11月-25日)</t>
         </is>
       </c>
       <c r="M15" s="21" t="inlineStr">
@@ -27148,7 +27148,7 @@
           <t>M | 272呎 (1房)
 $531万
 $19,514/呎
-(26年-05月-07日)</t>
+(26年-05月-08日)</t>
         </is>
       </c>
       <c r="N15" s="21" t="inlineStr">
@@ -27156,7 +27156,7 @@
           <t>N | 272呎 (1房)
 $531万
 $19,514/呎
-(26年-04月-21日)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="O15" s="21" t="inlineStr">
@@ -27164,7 +27164,7 @@
           <t>P | 268呎 (1房)
 $525万
 $19,572/呎
-(26年-04月-29日)</t>
+(26年-04月-30日)</t>
         </is>
       </c>
       <c r="P15" s="21" t="inlineStr">
@@ -27172,7 +27172,7 @@
           <t>Q | 367呎 (2房)
 $742万
 $20,226/呎
-(26年-04月-16日)</t>
+(26年-04月-17日)</t>
         </is>
       </c>
     </row>
@@ -27187,7 +27187,7 @@
           <t>A | 465呎 (3房)
 $878万
 $18,883/呎
-(25年-12月-28日)</t>
+(25年-12月-29日)</t>
         </is>
       </c>
       <c r="C16" s="21" t="inlineStr">
@@ -27195,7 +27195,7 @@
           <t>B | 349呎 (2房)
 $686万
 $19,662/呎
-(26年-03月-29日)</t>
+(26年-03月-30日)</t>
         </is>
       </c>
       <c r="D16" s="21" t="inlineStr">
@@ -27203,7 +27203,7 @@
           <t>C | 349呎 (2房)
 $688万
 $19,715/呎
-(26年-03月-23日)</t>
+(26年-03月-24日)</t>
         </is>
       </c>
       <c r="E16" s="21" t="inlineStr">
@@ -27211,7 +27211,7 @@
           <t>D | 349呎 (2房)
 $647万
 $18,529/呎
-(25年-10月-12日)</t>
+(25年-10月-13日)</t>
         </is>
       </c>
       <c r="F16" s="21" t="inlineStr">
@@ -27219,7 +27219,7 @@
           <t>E | 350呎 (2房)
 $650万
 $18,579/呎
-(25年-10月-08日)</t>
+(25年-10月-09日)</t>
         </is>
       </c>
       <c r="G16" s="21" t="inlineStr">
@@ -27227,7 +27227,7 @@
           <t>F | 269呎 (1房)
 $554万
 $20,584/呎
-(26年-05月-18日)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="H16" s="21" t="inlineStr">
@@ -27235,7 +27235,7 @@
           <t>G | 269呎 (1房)
 $536万
 $19,923/呎
-(26年-04月-09日)</t>
+(26年-04月-10日)</t>
         </is>
       </c>
       <c r="I16" s="21" t="inlineStr">
@@ -27243,7 +27243,7 @@
           <t>H | 379呎 (2房)
 $785万
 $20,713/呎
-(26年-04月-28日)</t>
+(26年-04月-29日)</t>
         </is>
       </c>
       <c r="J16" s="21" t="inlineStr">
@@ -27251,7 +27251,7 @@
           <t>J | 320呎 (2房)
 $595万
 $18,601/呎
-(25年-10月-09日)</t>
+(25年-10月-10日)</t>
         </is>
       </c>
       <c r="K16" s="21" t="inlineStr">
@@ -27259,7 +27259,7 @@
           <t>K | 269呎 (1房)
 $505万
 $18,783/呎
-(26年-03月-31日)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
       <c r="L16" s="21" t="inlineStr">
@@ -27267,7 +27267,7 @@
           <t>L | 272呎 (1房)
 $486万
 $17,852/呎
-(25年-10月-07日)</t>
+(25年-10月-08日)</t>
         </is>
       </c>
       <c r="M16" s="21" t="inlineStr">
@@ -27275,7 +27275,7 @@
           <t>M | 272呎 (1房)
 $529万
 $19,456/呎
-(26年-05月-13日)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="N16" s="21" t="inlineStr">
@@ -27283,7 +27283,7 @@
           <t>N | 272呎 (1房)
 $558万
 $20,497/呎
-(26年-04月-29日)</t>
+(26年-04月-30日)</t>
         </is>
       </c>
       <c r="O16" s="21" t="inlineStr">
@@ -27291,7 +27291,7 @@
           <t>P | 268呎 (1房)
 $523万
 $19,513/呎
-(26年-05月-06日)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="P16" s="21" t="inlineStr">
@@ -27299,7 +27299,7 @@
           <t>Q | 367呎 (2房)
 $736万
 $20,060/呎
-(26年-04月-12日)</t>
+(26年-04月-13日)</t>
         </is>
       </c>
     </row>
@@ -27314,7 +27314,7 @@
           <t>A | 465呎 (3房)
 $850万
 $18,283/呎
-(25年-10月-05日)</t>
+(25年-10月-06日)</t>
         </is>
       </c>
       <c r="C17" s="21" t="inlineStr">
@@ -27322,7 +27322,7 @@
           <t>B | 349呎 (2房)
 $682万
 $19,544/呎
-(26年-03月-26日)</t>
+(26年-03月-27日)</t>
         </is>
       </c>
       <c r="D17" s="21" t="inlineStr">
@@ -27330,7 +27330,7 @@
           <t>C | 349呎 (2房)
 $691万
 $19,807/呎
-(26年-03月-02日)</t>
+(26年-03月-03日)</t>
         </is>
       </c>
       <c r="E17" s="21" t="inlineStr">
@@ -27338,7 +27338,7 @@
           <t>D | 349呎 (2房)
 $678万
 $19,441/呎
-(25年-10月-02日)</t>
+(25年-10月-03日)</t>
         </is>
       </c>
       <c r="F17" s="21" t="inlineStr">
@@ -27346,7 +27346,7 @@
           <t>E | 350呎 (2房)
 $646万
 $18,468/呎
-(25年-10月-05日)</t>
+(25年-10月-06日)</t>
         </is>
       </c>
       <c r="G17" s="21" t="inlineStr">
@@ -27354,7 +27354,7 @@
           <t>F | 269呎 (1房)
 $551万
 $20,465/呎
-(26年-05月-21日)</t>
+(26年-05月-22日)</t>
         </is>
       </c>
       <c r="H17" s="21" t="inlineStr">
@@ -27362,7 +27362,7 @@
           <t>G | 269呎 (1房)
 $533万
 $19,809/呎
-(26年-03月-25日)</t>
+(26年-03月-26日)</t>
         </is>
       </c>
       <c r="I17" s="21" t="inlineStr">
@@ -27370,7 +27370,7 @@
           <t>H | 379呎 (2房)
 $725万
 $19,142/呎
-(25年-11月-13日)</t>
+(25年-11月-14日)</t>
         </is>
       </c>
       <c r="J17" s="21" t="inlineStr">
@@ -27378,7 +27378,7 @@
           <t>J | 320呎 (2房)
 $600万
 $18,748/呎
-(26年-03月-03日)</t>
+(26年-03月-04日)</t>
         </is>
       </c>
       <c r="K17" s="21" t="inlineStr">
@@ -27386,7 +27386,7 @@
           <t>K | 269呎 (1房)
 $504万
 $18,728/呎
-(26年-04月-01日)</t>
+(26年-04月-02日)</t>
         </is>
       </c>
       <c r="L17" s="21" t="inlineStr">
@@ -27394,7 +27394,7 @@
           <t>L | 272呎 (1房)
 $505万
 $18,581/呎
-(25年-10月-01日)</t>
+(25年-10月-02日)</t>
         </is>
       </c>
       <c r="M17" s="21" t="inlineStr">
@@ -27402,7 +27402,7 @@
           <t>M | 272呎 (1房)
 $528万
 $19,398/呎
-(26年-05月-05日)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
       <c r="N17" s="21" t="inlineStr">
@@ -27410,7 +27410,7 @@
           <t>N | 272呎 (1房)
 $528万
 $19,398/呎
-(26年-04月-26日)</t>
+(26年-04月-27日)</t>
         </is>
       </c>
       <c r="O17" s="21" t="inlineStr">
@@ -27418,7 +27418,7 @@
           <t>P | 268呎 (1房)
 $521万
 $19,453/呎
-(26年-05月-06日)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="P17" s="21" t="inlineStr">
@@ -27426,7 +27426,7 @@
           <t>Q | 367呎 (2房)
 $734万
 $19,999/呎
-(26年-03月-20日)</t>
+(26年-03月-21日)</t>
         </is>
       </c>
     </row>
@@ -27441,7 +27441,7 @@
           <t>A | 465呎 (3房)
 $916万
 $19,699/呎
-(25年-10月-08日)</t>
+(25年-10月-09日)</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
@@ -27449,7 +27449,7 @@
           <t>B | 349呎 (2房)
 $678万
 $19,426/呎
-(26年-03月-23日)</t>
+(26年-03月-24日)</t>
         </is>
       </c>
       <c r="D18" s="21" t="inlineStr">
@@ -27457,7 +27457,7 @@
           <t>C | 349呎 (2房)
 $680万
 $19,479/呎
-(26年-03月-01日)</t>
+(26年-03月-02日)</t>
         </is>
       </c>
       <c r="E18" s="21" t="inlineStr">
@@ -27465,7 +27465,7 @@
           <t>D | 349呎 (2房)
 $646万
 $18,513/呎
-(25年-10月-05日)</t>
+(25年-10月-06日)</t>
         </is>
       </c>
       <c r="F18" s="21" t="inlineStr">
@@ -27473,7 +27473,7 @@
           <t>E | 350呎 (2房)
 $678万
 $19,377/呎
-(25年-10月-12日)</t>
+(25年-10月-13日)</t>
         </is>
       </c>
       <c r="G18" s="21" t="inlineStr">
@@ -27481,7 +27481,7 @@
           <t>F | 269呎 (1房)
 $547万
 $20,347/呎
-(26年-05月-07日)</t>
+(26年-05月-08日)</t>
         </is>
       </c>
       <c r="H18" s="21" t="inlineStr">
@@ -27489,7 +27489,7 @@
           <t>G | 269呎 (1房)
 $558万
 $20,747/呎
-(26年-03月-12日)</t>
+(26年-03月-13日)</t>
         </is>
       </c>
       <c r="I18" s="21" t="inlineStr">
@@ -27497,7 +27497,7 @@
           <t>H | 379呎 (2房)
 $749万
 $19,766/呎
-(26年-03月-03日)</t>
+(26年-03月-04日)</t>
         </is>
       </c>
       <c r="J18" s="21" t="inlineStr">
@@ -27505,7 +27505,7 @@
           <t>J | 320呎 (2房)
 $598万
 $18,690/呎
-(26年-02月-19日)</t>
+(26年-02月-20日)</t>
         </is>
       </c>
       <c r="K18" s="21" t="inlineStr">
@@ -27513,7 +27513,7 @@
           <t>K | 269呎 (1房)
 $502万
 $18,668/呎
-(26年-04月-01日)</t>
+(26年-04月-02日)</t>
         </is>
       </c>
       <c r="L18" s="21" t="inlineStr">
@@ -27521,7 +27521,7 @@
           <t>L | 272呎 (1房)
 $504万
 $18,525/呎
-(25年-10月-13日)</t>
+(25年-10月-14日)</t>
         </is>
       </c>
       <c r="M18" s="21" t="inlineStr">
@@ -27529,7 +27529,7 @@
           <t>M | 272呎 (1房)
 $526万
 $19,339/呎
-(26年-05月-12日)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="N18" s="21" t="inlineStr">
@@ -27537,7 +27537,7 @@
           <t>N | 272呎 (1房)
 $526万
 $19,339/呎
-(26年-04月-20日)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="O18" s="21" t="inlineStr">
@@ -27545,7 +27545,7 @@
           <t>P | 268呎 (1房)
 $520万
 $19,394/呎
-(26年-05月-07日)</t>
+(26年-05月-08日)</t>
         </is>
       </c>
       <c r="P18" s="21" t="inlineStr">
@@ -27553,7 +27553,7 @@
           <t>Q | 367呎 (2房)
 $707万
 $19,270/呎
-(26年-03月-02日)</t>
+(26年-03月-03日)</t>
         </is>
       </c>
     </row>
@@ -27568,7 +27568,7 @@
           <t>A | 465呎 (3房)
 $916万
 $19,699/呎
-(25年-09月-25日)</t>
+(25年-09月-26日)</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
@@ -27576,7 +27576,7 @@
           <t>B | 349呎 (2房)
 $667万
 $19,114/呎
-(26年-01月-11日)</t>
+(26年-01月-12日)</t>
         </is>
       </c>
       <c r="D19" s="21" t="inlineStr">
@@ -27584,7 +27584,7 @@
           <t>C | 349呎 (2房)
 $669万
 $19,167/呎
-(26年-02月-22日)</t>
+(26年-02月-23日)</t>
         </is>
       </c>
       <c r="E19" s="21" t="inlineStr">
@@ -27592,7 +27592,7 @@
           <t>D | 349呎 (2房)
 $639万
 $18,309/呎
-(25年-10月-08日)</t>
+(25年-10月-09日)</t>
         </is>
       </c>
       <c r="F19" s="21" t="inlineStr">
@@ -27600,7 +27600,7 @@
           <t>E | 350呎 (2房)
 $650万
 $18,561/呎
-(25年-10月-05日)</t>
+(25年-10月-06日)</t>
         </is>
       </c>
       <c r="G19" s="21" t="inlineStr">
@@ -27608,7 +27608,7 @@
           <t>F | 269呎 (1房)
 $547万
 $20,347/呎
-(26年-05月-17日)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="H19" s="21" t="inlineStr">
@@ -27616,7 +27616,7 @@
           <t>G | 269呎 (1房)
 $530万
 $19,694/呎
-(26年-03月-30日)</t>
+(26年-03月-31日)</t>
         </is>
       </c>
       <c r="I19" s="21" t="inlineStr">
@@ -27624,7 +27624,7 @@
           <t>H | 379呎 (2房)
 $789万
 $20,823/呎
-(26年-04月-12日)</t>
+(26年-04月-13日)</t>
         </is>
       </c>
       <c r="J19" s="21" t="inlineStr">
@@ -27632,7 +27632,7 @@
           <t>J | 320呎 (2房)
 $640万
 $20,011/呎
-(26年-03月-16日)</t>
+(26年-03月-17日)</t>
         </is>
       </c>
       <c r="K19" s="21" t="inlineStr">
@@ -27640,7 +27640,7 @@
           <t>K | 269呎 (1房)
 $502万
 $18,668/呎
-(26年-04月-09日)</t>
+(26年-04月-10日)</t>
         </is>
       </c>
       <c r="L19" s="21" t="inlineStr">
@@ -27648,7 +27648,7 @@
           <t>L | 272呎 (1房)
 $504万
 $18,525/呎
-(25年-09月-13日)</t>
+(25年-09月-14日)</t>
         </is>
       </c>
       <c r="M19" s="21" t="inlineStr">
@@ -27656,7 +27656,7 @@
           <t>M | 272呎 (1房)
 $526万
 $19,339/呎
-(26年-04月-28日)</t>
+(26年-04月-29日)</t>
         </is>
       </c>
       <c r="N19" s="21" t="inlineStr">
@@ -27664,7 +27664,7 @@
           <t>N | 272呎 (1房)
 $532万
 $19,546/呎
-(26年-04月-26日)</t>
+(26年-04月-27日)</t>
         </is>
       </c>
       <c r="O19" s="21" t="inlineStr">
@@ -27672,7 +27672,7 @@
           <t>P | 268呎 (1房)
 $520万
 $19,394/呎
-(26年-04月-29日)</t>
+(26年-04月-30日)</t>
         </is>
       </c>
       <c r="P19" s="21" t="inlineStr">
@@ -27680,7 +27680,7 @@
           <t>Q | 367呎 (2房)
 $726万
 $19,793/呎
-(26年-03月-16日)</t>
+(26年-03月-17日)</t>
         </is>
       </c>
     </row>
@@ -27695,7 +27695,7 @@
           <t>A | 465呎 (3房)
 $862万
 $18,542/呎
-(25年-11月-04日)</t>
+(25年-11月-05日)</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
@@ -27703,7 +27703,7 @@
           <t>B | 349呎 (2房)
 $659万
 $18,882/呎
-(26年-02月-09日)</t>
+(26年-02月-10日)</t>
         </is>
       </c>
       <c r="D20" s="21" t="inlineStr">
@@ -27711,7 +27711,7 @@
           <t>C | 349呎 (2房)
 $661万
 $18,935/呎
-(26年-01月-27日)</t>
+(26年-01月-28日)</t>
         </is>
       </c>
       <c r="E20" s="21" t="inlineStr">
@@ -27719,7 +27719,7 @@
           <t>D | 349呎 (2房)
 $631万
 $18,088/呎
-(25年-10月-08日)</t>
+(25年-10月-09日)</t>
         </is>
       </c>
       <c r="F20" s="21" t="inlineStr">
@@ -27727,7 +27727,7 @@
           <t>E | 350呎 (2房)
 $635万
 $18,139/呎
-(25年-10月-13日)</t>
+(25年-10月-14日)</t>
         </is>
       </c>
       <c r="G20" s="21" t="inlineStr">
@@ -27735,7 +27735,7 @@
           <t>F | 269呎 (1房)
 $533万
 $19,824/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
       <c r="H20" s="21" t="inlineStr">
@@ -27743,7 +27743,7 @@
           <t>G | 269呎 (1房)
 $524万
 $19,465/呎
-(26年-03月-31日)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
       <c r="I20" s="21" t="inlineStr">
@@ -27751,7 +27751,7 @@
           <t>H | 379呎 (2房)
 $740万
 $19,529/呎
-(26年-03月-19日)</t>
+(26年-03月-20日)</t>
         </is>
       </c>
       <c r="J20" s="21" t="inlineStr">
@@ -27759,7 +27759,7 @@
           <t>J | 320呎 (2房)
 $627万
 $19,585/呎
-(26年-02月-11日)</t>
+(26年-02月-12日)</t>
         </is>
       </c>
       <c r="K20" s="21" t="inlineStr">
@@ -27767,7 +27767,7 @@
           <t>K | 269呎 (1房)
 $499万
 $18,554/呎
-(26年-03月-30日)</t>
+(26年-03月-31日)</t>
         </is>
       </c>
       <c r="L20" s="21" t="inlineStr">
@@ -27775,7 +27775,7 @@
           <t>L | 272呎 (1房)
 $501万
 $18,413/呎
-(25年-10月-08日)</t>
+(25年-10月-09日)</t>
         </is>
       </c>
       <c r="M20" s="21" t="inlineStr">
@@ -27783,7 +27783,7 @@
           <t>M | 272呎 (1房)
 $513万
 $18,848/呎
-(26年-04月-16日)</t>
+(26年-04月-17日)</t>
         </is>
       </c>
       <c r="N20" s="21" t="inlineStr">
@@ -27791,7 +27791,7 @@
           <t>N | 272呎 (1房)
 $551万
 $20,250/呎
-(26年-05月-14日)</t>
+(26年-05月-15日)</t>
         </is>
       </c>
       <c r="O20" s="21" t="inlineStr">
@@ -27799,7 +27799,7 @@
           <t>P | 268呎 (1房)
 $522万
 $19,482/呎
-(26年-05月-11日)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="P20" s="21" t="inlineStr">
@@ -27807,7 +27807,7 @@
           <t>Q | 367呎 (2房)
 $721万
 $19,657/呎
-(25年-10月-09日)</t>
+(25年-10月-10日)</t>
         </is>
       </c>
     </row>
@@ -27822,7 +27822,7 @@
           <t>A | 465呎 (3房)
 $900万
 $19,347/呎
-(25年-10月-13日)</t>
+(25年-10月-14日)</t>
         </is>
       </c>
       <c r="C21" s="21" t="inlineStr">
@@ -27830,7 +27830,7 @@
           <t>B | 349呎 (2房)
 $655万
 $18,766/呎
-(26年-01月-20日)</t>
+(26年-01月-21日)</t>
         </is>
       </c>
       <c r="D21" s="21" t="inlineStr">
@@ -27838,7 +27838,7 @@
           <t>C | 349呎 (2房)
 $664万
 $19,023/呎
-(26年-02月-08日)</t>
+(26年-02月-09日)</t>
         </is>
       </c>
       <c r="E21" s="21" t="inlineStr">
@@ -27846,7 +27846,7 @@
           <t>D | 349呎 (2房)
 $627万
 $17,977/呎
-(25年-10月-01日)</t>
+(25年-10月-02日)</t>
         </is>
       </c>
       <c r="F21" s="21" t="inlineStr">
@@ -27854,7 +27854,7 @@
           <t>E | 350呎 (2房)
 $631万
 $18,028/呎
-(25年-10月-08日)</t>
+(25年-10月-09日)</t>
         </is>
       </c>
       <c r="G21" s="21" t="inlineStr">
@@ -27862,7 +27862,7 @@
           <t>F | 269呎 (1房)
 $527万
 $19,600/呎
-(26年-04月-15日)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
       <c r="H21" s="21" t="inlineStr">
@@ -27870,7 +27870,7 @@
           <t>G | 269呎 (1房)
 $548万
 $20,384/呎
-(26年-03月-05日)</t>
+(26年-03月-06日)</t>
         </is>
       </c>
       <c r="I21" s="21" t="inlineStr">
@@ -27878,7 +27878,7 @@
           <t>H | 379呎 (2房)
 $743万
 $19,616/呎
-(26年-04月-16日)</t>
+(26年-04月-17日)</t>
         </is>
       </c>
       <c r="J21" s="21" t="inlineStr">
@@ -27886,7 +27886,7 @@
           <t>J | 320呎 (2房)
 $599万
 $18,722/呎
-(26年-02月-09日)</t>
+(26年-02月-10日)</t>
         </is>
       </c>
       <c r="K21" s="21" t="inlineStr">
@@ -27894,7 +27894,7 @@
           <t>K | 269呎 (1房)
 $498万
 $18,498/呎
-(26年-03月-29日)</t>
+(26年-03月-30日)</t>
         </is>
       </c>
       <c r="L21" s="21" t="inlineStr">
@@ -27902,7 +27902,7 @@
           <t>L | 272呎 (1房)
 $499万
 $18,357/呎
-(25年-10月-05日)</t>
+(25年-10月-06日)</t>
         </is>
       </c>
       <c r="M21" s="21" t="inlineStr">
@@ -27910,7 +27910,7 @@
           <t>M | 272呎 (1房)
 $517万
 $18,990/呎
-(26年-04月-19日)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
       <c r="N21" s="21" t="inlineStr">
@@ -27918,7 +27918,7 @@
           <t>N | 272呎 (1房)
 $521万
 $19,164/呎
-(26年-05月-14日)</t>
+(26年-05月-15日)</t>
         </is>
       </c>
       <c r="O21" s="21" t="inlineStr">
@@ -27926,7 +27926,7 @@
           <t>P | 268呎 (1房)
 $515万
 $19,216/呎
-(26年-04月-12日)</t>
+(26年-04月-13日)</t>
         </is>
       </c>
       <c r="P21" s="21" t="inlineStr">
@@ -27934,7 +27934,7 @@
           <t>Q | 367呎 (2房)
 $694万
 $18,921/呎
-(26年-03月-01日)</t>
+(26年-03月-02日)</t>
         </is>
       </c>
     </row>
@@ -27949,7 +27949,7 @@
           <t>A | 465呎 (3房)
 $894万
 $19,231/呎
-(25年-10月-08日)</t>
+(25年-10月-09日)</t>
         </is>
       </c>
       <c r="C22" s="21" t="inlineStr">
@@ -27957,7 +27957,7 @@
           <t>B | 349呎 (2房)
 $672万
 $19,258/呎
-(25年-10月-07日)</t>
+(25年-10月-08日)</t>
         </is>
       </c>
       <c r="D22" s="21" t="inlineStr">
@@ -27965,7 +27965,7 @@
           <t>C | 349呎 (2房)
 $646万
 $18,500/呎
-(25年-11月-09日)</t>
+(25年-11月-10日)</t>
         </is>
       </c>
       <c r="E22" s="21" t="inlineStr">
@@ -27973,7 +27973,7 @@
           <t>D | 349呎 (2房)
 $624万
 $17,866/呎
-(25年-10月-02日)</t>
+(25年-10月-03日)</t>
         </is>
       </c>
       <c r="F22" s="21" t="inlineStr">
@@ -27981,7 +27981,7 @@
           <t>E | 350呎 (2房)
 $662万
 $18,913/呎
-(25年-10月-07日)</t>
+(25年-10月-08日)</t>
         </is>
       </c>
       <c r="G22" s="21" t="inlineStr">
@@ -27989,7 +27989,7 @@
           <t>F | 269呎 (1房)
 $524万
 $19,486/呎
-(26年-04月-16日)</t>
+(26年-04月-17日)</t>
         </is>
       </c>
       <c r="H22" s="21" t="inlineStr">
@@ -27997,7 +27997,7 @@
           <t>G | 269呎 (1房)
 $523万
 $19,441/呎
-(26年-03月-04日)</t>
+(26年-03月-05日)</t>
         </is>
       </c>
       <c r="I22" s="21" t="inlineStr">
@@ -28005,7 +28005,7 @@
           <t>H | 379呎 (2房)
 $731万
 $19,289/呎
-(26年-04月-19日)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
       <c r="J22" s="21" t="inlineStr">
@@ -28013,7 +28013,7 @@
           <t>J | 320呎 (2房)
 $574万
 $17,949/呎
-(25年-12月-07日)</t>
+(25年-12月-08日)</t>
         </is>
       </c>
       <c r="K22" s="21" t="inlineStr">
@@ -28021,7 +28021,7 @@
           <t>K | 269呎 (1房)
 $519万
 $19,304/呎
-(26年-03月-26日)</t>
+(26年-03月-27日)</t>
         </is>
       </c>
       <c r="L22" s="21" t="inlineStr">
@@ -28029,7 +28029,7 @@
           <t>L | 272呎 (1房)
 $469万
 $17,232/呎
-(25年-10月-01日)</t>
+(25年-10月-02日)</t>
         </is>
       </c>
       <c r="M22" s="21" t="inlineStr">
@@ -28037,7 +28037,7 @@
           <t>M | 272呎 (1房)
 $506万
 $18,617/呎
-(26年-04月-13日)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
       <c r="N22" s="21" t="inlineStr">
@@ -28045,7 +28045,7 @@
           <t>N | 272呎 (1房)
 $516万
 $18,989/呎
-(26年-05月-14日)</t>
+(26年-05月-15日)</t>
         </is>
       </c>
       <c r="O22" s="21" t="inlineStr">
@@ -28053,7 +28053,7 @@
           <t>P | 268呎 (1房)
 $510万
 $19,035/呎
-(26年-05月-03日)</t>
+(26年-05月-04日)</t>
         </is>
       </c>
       <c r="P22" s="21" t="inlineStr">
@@ -28061,7 +28061,7 @@
           <t>Q | 367呎 (2房)
 $728万
 $19,828/呎
-(26年-03月-01日)</t>
+(26年-03月-02日)</t>
         </is>
       </c>
     </row>
@@ -28076,7 +28076,7 @@
           <t>A | 465呎 (3房)
 $889万
 $19,114/呎
-(25年-10月-08日)</t>
+(25年-10月-09日)</t>
         </is>
       </c>
       <c r="C23" s="21" t="inlineStr">
@@ -28084,7 +28084,7 @@
           <t>B | 349呎 (2房)
 $668万
 $19,139/呎
-(25年-12月-18日)</t>
+(25年-12月-19日)</t>
         </is>
       </c>
       <c r="D23" s="21" t="inlineStr">
@@ -28092,7 +28092,7 @@
           <t>C | 349呎 (2房)
 $634万
 $18,162/呎
-(25年-12月-14日)</t>
+(25年-12月-15日)</t>
         </is>
       </c>
       <c r="E23" s="21" t="inlineStr">
@@ -28100,7 +28100,7 @@
           <t>D | 349呎 (2房)
 $620万
 $17,755/呎
-(25年-10月-09日)</t>
+(25年-10月-10日)</t>
         </is>
       </c>
       <c r="F23" s="21" t="inlineStr">
@@ -28108,7 +28108,7 @@
           <t>E | 350呎 (2房)
 $665万
 $18,994/呎
-(25年-10月-07日)</t>
+(25年-10月-08日)</t>
         </is>
       </c>
       <c r="G23" s="21" t="inlineStr">
@@ -28116,7 +28116,7 @@
           <t>F | 269呎 (1房)
 $521万
 $19,367/呎
-(26年-04月-08日)</t>
+(26年-04月-09日)</t>
         </is>
       </c>
       <c r="H23" s="21" t="inlineStr">
@@ -28124,7 +28124,7 @@
           <t>G | 269呎 (1房)
 $514万
 $19,120/呎
-(26年-03月-16日)</t>
+(26年-03月-17日)</t>
         </is>
       </c>
       <c r="I23" s="21" t="inlineStr">
@@ -28132,7 +28132,7 @@
           <t>H | 379呎 (2房)
 $734万
 $19,374/呎
-(26年-04月-01日)</t>
+(26年-04月-02日)</t>
         </is>
       </c>
       <c r="J23" s="21" t="inlineStr">
@@ -28140,7 +28140,7 @@
           <t>J | 320呎 (2房)
 $585万
 $18,291/呎
-(26年-02月-08日)</t>
+(26年-02月-09日)</t>
         </is>
       </c>
       <c r="K23" s="21" t="inlineStr">
@@ -28148,7 +28148,7 @@
           <t>K | 269呎 (1房)
 $491万
 $18,269/呎
-(26年-03月-31日)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
       <c r="L23" s="21" t="inlineStr">
@@ -28156,7 +28156,7 @@
           <t>L | 272呎 (1房)
 $467万
 $17,179/呎
-(25年-09月-28日)</t>
+(25年-09月-29日)</t>
         </is>
       </c>
       <c r="M23" s="21" t="inlineStr">
@@ -28164,7 +28164,7 @@
           <t>M | 272呎 (1房)
 $505万
 $18,559/呎
-(26年-04月-13日)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
       <c r="N23" s="21" t="inlineStr">
@@ -28172,7 +28172,7 @@
           <t>N | 272呎 (1房)
 $518万
 $19,031/呎
-(26年-04月-26日)</t>
+(26年-04月-27日)</t>
         </is>
       </c>
       <c r="O23" s="21" t="inlineStr">
@@ -28180,7 +28180,7 @@
           <t>P | 268呎 (1房)
 $509万
 $18,975/呎
-(26年-05月-07日)</t>
+(26年-05月-08日)</t>
         </is>
       </c>
       <c r="P23" s="21" t="inlineStr">
@@ -28188,7 +28188,7 @@
           <t>Q | 367呎 (2房)
 $671万
 $18,284/呎
-(25年-10月-08日)</t>
+(25年-10月-09日)</t>
         </is>
       </c>
     </row>
@@ -28203,7 +28203,7 @@
           <t>A | 465呎 (3房)
 $832万
 $17,886/呎
-(25年-10月-07日)</t>
+(25年-10月-08日)</t>
         </is>
       </c>
       <c r="C24" s="21" t="inlineStr">
@@ -28211,7 +28211,7 @@
           <t>B | 349呎 (2房)
 $625万
 $17,905/呎
-(25年-12月-10日)</t>
+(25年-12月-11日)</t>
         </is>
       </c>
       <c r="D24" s="21" t="inlineStr">
@@ -28219,7 +28219,7 @@
           <t>C | 349呎 (2房)
 $661万
 $18,926/呎
-(25年-12月-14日)</t>
+(25年-12月-15日)</t>
         </is>
       </c>
       <c r="E24" s="21" t="inlineStr">
@@ -28227,7 +28227,7 @@
           <t>D | 349呎 (2房)
 $646万
 $18,510/呎
-(25年-10月-08日)</t>
+(25年-10月-09日)</t>
         </is>
       </c>
       <c r="F24" s="21" t="inlineStr">
@@ -28235,7 +28235,7 @@
           <t>E | 350呎 (2房)
 $650万
 $18,563/呎
-(25年-09月-13日)</t>
+(25年-09月-14日)</t>
         </is>
       </c>
       <c r="G24" s="21" t="inlineStr">
@@ -28243,7 +28243,7 @@
           <t>F | 269呎 (1房)
 $515万
 $19,134/呎
-(26年-04月-16日)</t>
+(26年-04月-17日)</t>
         </is>
       </c>
       <c r="H24" s="21" t="inlineStr">
@@ -28251,7 +28251,7 @@
           <t>G | 269呎 (1房)
 $508万
 $18,891/呎
-(26年-03月-16日)</t>
+(26年-03月-17日)</t>
         </is>
       </c>
       <c r="I24" s="21" t="inlineStr">
@@ -28259,7 +28259,7 @@
           <t>H | 379呎 (2房)
 $756万
 $19,944/呎
-(26年-04月-15日)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
       <c r="J24" s="21" t="inlineStr">
@@ -28267,7 +28267,7 @@
           <t>J | 320呎 (2房)
 $571万
 $17,840/呎
-(25年-10月-09日)</t>
+(25年-10月-10日)</t>
         </is>
       </c>
       <c r="K24" s="21" t="inlineStr">
@@ -28275,7 +28275,7 @@
           <t>K | 269呎 (1房)
 $492万
 $18,307/呎
-(26年-03月-31日)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
       <c r="L24" s="21" t="inlineStr">
@@ -28283,7 +28283,7 @@
           <t>L | 272呎 (1房)
 $492万
 $18,078/呎
-(25年-10月-08日)</t>
+(25年-10月-09日)</t>
         </is>
       </c>
       <c r="M24" s="21" t="inlineStr">
@@ -28291,7 +28291,7 @@
           <t>M | 272呎 (1房)
 $503万
 $18,500/呎
-(26年-04月-14日)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="N24" s="21" t="inlineStr">
@@ -28299,7 +28299,7 @@
           <t>N | 272呎 (1房)
 $519万
 $19,070/呎
-(26年-04月-27日)</t>
+(26年-04月-28日)</t>
         </is>
       </c>
       <c r="O24" s="21" t="inlineStr">
@@ -28307,7 +28307,7 @@
           <t>P | 268呎 (1房)
 $507万
 $18,916/呎
-(26年-05月-07日)</t>
+(26年-05月-08日)</t>
         </is>
       </c>
       <c r="P24" s="21" t="inlineStr">
@@ -28315,7 +28315,7 @@
           <t>Q | 367呎 (2房)
 $667万
 $18,172/呎
-(25年-10月-05日)</t>
+(25年-10月-06日)</t>
         </is>
       </c>
     </row>
@@ -28330,7 +28330,7 @@
           <t>A | 465呎 (3房)
 $816万
 $17,555/呎
-(25年-10月-12日)</t>
+(25年-10月-13日)</t>
         </is>
       </c>
       <c r="C25" s="21" t="inlineStr">
@@ -28338,7 +28338,7 @@
           <t>B | 349呎 (2房)
 $613万
 $17,564/呎
-(25年-12月-04日)</t>
+(25年-12月-05日)</t>
         </is>
       </c>
       <c r="D25" s="21" t="inlineStr">
@@ -28346,7 +28346,7 @@
           <t>C | 349呎 (2房)
 $648万
 $18,567/呎
-(25年-10月-20日)</t>
+(25年-10月-21日)</t>
         </is>
       </c>
       <c r="E25" s="21" t="inlineStr">
@@ -28354,7 +28354,7 @@
           <t>D | 349呎 (2房)
 $634万
 $18,159/呎
-(25年-10月-09日)</t>
+(25年-10月-10日)</t>
         </is>
       </c>
       <c r="F25" s="21" t="inlineStr">
@@ -28362,7 +28362,7 @@
           <t>E | 350呎 (2房)
 $638万
 $18,215/呎
-(25年-10月-09日)</t>
+(25年-10月-10日)</t>
         </is>
       </c>
       <c r="G25" s="21" t="inlineStr">
@@ -28370,7 +28370,7 @@
           <t>F | 269呎 (1房)
 $505万
 $18,787/呎
-(26年-04月-14日)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="H25" s="21" t="inlineStr">
@@ -28378,7 +28378,7 @@
           <t>G | 269呎 (1房)
 $488万
 $18,150/呎
-(25年-12月-08日)</t>
+(25年-12月-09日)</t>
         </is>
       </c>
       <c r="I25" s="21" t="inlineStr">
@@ -28386,7 +28386,7 @@
           <t>H | 379呎 (2房)
 $708万
 $18,671/呎
-(26年-03月-19日)</t>
+(26年-03月-20日)</t>
         </is>
       </c>
       <c r="J25" s="21" t="inlineStr">
@@ -28394,7 +28394,7 @@
           <t>J | 320呎 (2房)
 $582万
 $18,178/呎
-(26年-02月-08日)</t>
+(26年-02月-09日)</t>
         </is>
       </c>
       <c r="K25" s="21" t="inlineStr">
@@ -28402,7 +28402,7 @@
           <t>K | 269呎 (1房)
 $488万
 $18,154/呎
-(26年-03月-31日)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
       <c r="L25" s="21" t="inlineStr">
@@ -28410,7 +28410,7 @@
           <t>L | 272呎 (1房)
 $490万
 $18,018/呎
-(25年-10月-08日)</t>
+(25年-10月-09日)</t>
         </is>
       </c>
       <c r="M25" s="21" t="inlineStr">
@@ -28418,7 +28418,7 @@
           <t>M | 272呎 (1房)
 $502万
 $18,446/呎
-(26年-04月-14日)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="N25" s="21" t="inlineStr">
@@ -28426,7 +28426,7 @@
           <t>N | 272呎 (1房)
 $512万
 $18,810/呎
-(26年-04月-27日)</t>
+(26年-04月-28日)</t>
         </is>
       </c>
       <c r="O25" s="21" t="inlineStr">
@@ -28434,7 +28434,7 @@
           <t>P | 268呎 (1房)
 $506万
 $18,892/呎
-(26年-04月-26日)</t>
+(26年-04月-27日)</t>
         </is>
       </c>
       <c r="P25" s="21" t="inlineStr">
@@ -28442,7 +28442,7 @@
           <t>Q | 367呎 (2房)
 $663万
 $18,056/呎
-(25年-10月-09日)</t>
+(25年-10月-10日)</t>
         </is>
       </c>
     </row>
@@ -28457,7 +28457,7 @@
           <t>A | 465呎 (3房)
 $818万
 $17,582/呎
-(25年-10月-09日)</t>
+(25年-10月-10日)</t>
         </is>
       </c>
       <c r="C26" s="21" t="inlineStr">
@@ -28465,7 +28465,7 @@
           <t>B | 349呎 (2房)
 $621万
 $17,781/呎
-(26年-01月-08日)</t>
+(26年-01月-09日)</t>
         </is>
       </c>
       <c r="D26" s="21" t="inlineStr">
@@ -28473,7 +28473,7 @@
           <t>C | 349呎 (2房)
 $621万
 $17,807/呎
-(26年-01月-29日)</t>
+(26年-01月-30日)</t>
         </is>
       </c>
       <c r="E26" s="21" t="inlineStr">
@@ -28481,7 +28481,7 @@
           <t>D | 349呎 (2房)
 $595万
 $17,038/呎
-(25年-10月-05日)</t>
+(25年-10月-06日)</t>
         </is>
       </c>
       <c r="F26" s="21" t="inlineStr">
@@ -28489,7 +28489,7 @@
           <t>E | 350呎 (2房)
 $631万
 $18,039/呎
-(25年-10月-09日)</t>
+(25年-10月-10日)</t>
         </is>
       </c>
       <c r="G26" s="21" t="inlineStr">
@@ -28497,7 +28497,7 @@
           <t>F | 269呎 (1房)
 $501万
 $18,609/呎
-(26年-04月-16日)</t>
+(26年-04月-17日)</t>
         </is>
       </c>
       <c r="H26" s="21" t="inlineStr">
@@ -28505,7 +28505,7 @@
           <t>G | 269呎 (1房)
 $492万
 $18,278/呎
-(26年-01月-12日)</t>
+(26年-01月-13日)</t>
         </is>
       </c>
       <c r="I26" s="21" t="inlineStr">
@@ -28513,7 +28513,7 @@
           <t>H | 379呎 (2房)
 $734万
 $19,378/呎
-(26年-03月-03日)</t>
+(26年-03月-04日)</t>
         </is>
       </c>
       <c r="J26" s="21" t="inlineStr">
@@ -28521,7 +28521,7 @@
           <t>J | 320呎 (2房)
 $567万
 $17,727/呎
-(25年-12月-10日)</t>
+(25年-12月-11日)</t>
         </is>
       </c>
       <c r="K26" s="21" t="inlineStr">
@@ -28529,7 +28529,7 @@
           <t>K | 269呎 (1房)
 $487万
 $18,095/呎
-(26年-04月-16日)</t>
+(26年-04月-17日)</t>
         </is>
       </c>
       <c r="L26" s="21" t="inlineStr">
@@ -28537,7 +28537,7 @@
           <t>L | 272呎 (1房)
 $465万
 $17,112/呎
-(25年-11月-06日)</t>
+(25年-11月-07日)</t>
         </is>
       </c>
       <c r="M26" s="21" t="inlineStr">
@@ -28545,7 +28545,7 @@
           <t>M | 272呎 (1房)
 $500万
 $18,387/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
       <c r="N26" s="21" t="inlineStr">
@@ -28553,7 +28553,7 @@
           <t>N | 272呎 (1房)
 $510万
 $18,751/呎
-(26年-04月-22日)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="O26" s="21" t="inlineStr">
@@ -28561,7 +28561,7 @@
           <t>P | 268呎 (1房)
 $505万
 $18,832/呎
-(26年-05月-05日)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
       <c r="P26" s="21" t="inlineStr">
@@ -28569,7 +28569,7 @@
           <t>Q | 367呎 (2房)
 $656万
 $17,887/呎
-(25年-11月-26日)</t>
+(25年-11月-27日)</t>
         </is>
       </c>
     </row>
@@ -28584,7 +28584,7 @@
           <t>A | 465呎 (3房)
 $796万
 $17,122/呎
-(25年-10月-05日)</t>
+(25年-10月-06日)</t>
         </is>
       </c>
       <c r="C27" s="21" t="inlineStr">
@@ -28592,7 +28592,7 @@
           <t>B | 349呎 (2房)
 $621万
 $17,781/呎
-(26年-01月-15日)</t>
+(26年-01月-16日)</t>
         </is>
       </c>
       <c r="D27" s="21" t="inlineStr">
@@ -28600,7 +28600,7 @@
           <t>C | 349呎 (2房)
 $662万
 $18,968/呎
-(26年-01月-08日)</t>
+(26年-01月-09日)</t>
         </is>
       </c>
       <c r="E27" s="21" t="inlineStr">
@@ -28608,7 +28608,7 @@
           <t>D | 349呎 (2房)
 $595万
 $17,038/呎
-(25年-10月-08日)</t>
+(25年-10月-09日)</t>
         </is>
       </c>
       <c r="F27" s="21" t="inlineStr">
@@ -28616,7 +28616,7 @@
           <t>E | 350呎 (2房)
 $598万
 $17,090/呎
-(25年-10月-09日)</t>
+(25年-10月-10日)</t>
         </is>
       </c>
       <c r="G27" s="21" t="inlineStr">
@@ -28624,7 +28624,7 @@
           <t>F | 269呎 (1房)
 $501万
 $18,609/呎
-(26年-04月-09日)</t>
+(26年-04月-10日)</t>
         </is>
       </c>
       <c r="H27" s="21" t="inlineStr">
@@ -28632,7 +28632,7 @@
           <t>G | 269呎 (1房)
 $486万
 $18,082/呎
-(26年-02月-15日)</t>
+(26年-02月-16日)</t>
         </is>
       </c>
       <c r="I27" s="21" t="inlineStr">
@@ -28640,7 +28640,7 @@
           <t>H | 379呎 (2房)
 $705万
 $18,591/呎
-(26年-03月-25日)</t>
+(26年-03月-26日)</t>
         </is>
       </c>
       <c r="J27" s="21" t="inlineStr">
@@ -28648,7 +28648,7 @@
           <t>J | 320呎 (2房)
 $580万
 $18,121/呎
-(26年-02月-10日)</t>
+(26年-02月-11日)</t>
         </is>
       </c>
       <c r="K27" s="21" t="inlineStr">
@@ -28656,7 +28656,7 @@
           <t>K | 269呎 (1房)
 $487万
 $18,095/呎
-(26年-03月-31日)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
       <c r="L27" s="21" t="inlineStr">
@@ -28664,7 +28664,7 @@
           <t>L | 272呎 (1房)
 $463万
 $17,017/呎
-(25年-10月-09日)</t>
+(25年-10月-10日)</t>
         </is>
       </c>
       <c r="M27" s="21" t="inlineStr">
@@ -28672,7 +28672,7 @@
           <t>M | 272呎 (1房)
 $500万
 $18,387/呎
-(26年-04月-16日)</t>
+(26年-04月-17日)</t>
         </is>
       </c>
       <c r="N27" s="21" t="inlineStr">
@@ -28680,7 +28680,7 @@
           <t>N | 272呎 (1房)
 $510万
 $18,751/呎
-(26年-04月-27日)</t>
+(26年-04月-28日)</t>
         </is>
       </c>
       <c r="O27" s="21" t="inlineStr">
@@ -28688,7 +28688,7 @@
           <t>P | 268呎 (1房)
 $532万
 $19,840/呎
-(26年-04月-29日)</t>
+(26年-04月-30日)</t>
         </is>
       </c>
       <c r="P27" s="21" t="inlineStr">
@@ -28696,7 +28696,7 @@
           <t>Q | 367呎 (2房)
 $671万
 $18,284/呎
-(26年-02月-24日)</t>
+(26年-02月-25日)</t>
         </is>
       </c>
     </row>
@@ -28711,7 +28711,7 @@
           <t>A | 465呎 (3房)
 $772万
 $16,610/呎
-(25年-10月-09日)</t>
+(25年-10月-10日)</t>
         </is>
       </c>
       <c r="C28" s="21" t="inlineStr">
@@ -28719,7 +28719,7 @@
           <t>B | 349呎 (2房)
 $615万
 $17,622/呎
-(26年-02月-05日)</t>
+(26年-02月-06日)</t>
         </is>
       </c>
       <c r="D28" s="21" t="inlineStr">
@@ -28727,7 +28727,7 @@
           <t>C | 349呎 (2房)
 $609万
 $17,459/呎
-(26年-02月-12日)</t>
+(26年-02月-13日)</t>
         </is>
       </c>
       <c r="E28" s="21" t="inlineStr">
@@ -28735,7 +28735,7 @@
           <t>D | 349呎 (2房)
 $622万
 $17,819/呎
-(25年-10月-02日)</t>
+(25年-10月-03日)</t>
         </is>
       </c>
       <c r="F28" s="21" t="inlineStr">
@@ -28743,7 +28743,7 @@
           <t>E | 350呎 (2房)
 $626万
 $17,878/呎
-(25年-10月-08日)</t>
+(25年-10月-09日)</t>
         </is>
       </c>
       <c r="G28" s="21" t="inlineStr">
@@ -28751,7 +28751,7 @@
           <t>F | 269呎 (1房)
 $491万
 $18,262/呎
-(26年-04月-12日)</t>
+(26年-04月-13日)</t>
         </is>
       </c>
       <c r="H28" s="21" t="inlineStr">
@@ -28759,7 +28759,7 @@
           <t>G | 269呎 (1房)
 $498万
 $18,514/呎
-(25年-10月-08日)</t>
+(25年-10月-09日)</t>
         </is>
       </c>
       <c r="I28" s="21" t="inlineStr">
@@ -28767,7 +28767,7 @@
           <t>H | 379呎 (2房)
 $658万
 $17,361/呎
-(25年-10月-02日)</t>
+(25年-10月-03日)</t>
         </is>
       </c>
       <c r="J28" s="21" t="inlineStr">
@@ -28775,7 +28775,7 @@
           <t>J | 320呎 (2房)
 $576万
 $18,006/呎
-(26年-02月-10日)</t>
+(26年-02月-11日)</t>
         </is>
       </c>
       <c r="K28" s="21" t="inlineStr">
@@ -28783,7 +28783,7 @@
           <t>K | 269呎 (1房)
 $484万
 $17,980/呎
-(26年-04月-16日)</t>
+(26年-04月-17日)</t>
         </is>
       </c>
       <c r="L28" s="21" t="inlineStr">
@@ -28791,7 +28791,7 @@
           <t>L | 272呎 (1房)
 $491万
 $18,039/呎
-(25年-10月-05日)</t>
+(25年-10月-06日)</t>
         </is>
       </c>
       <c r="M28" s="21" t="inlineStr">
@@ -28799,7 +28799,7 @@
           <t>M | 272呎 (1房)
 $497万
 $18,270/呎
-(26年-04月-13日)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
       <c r="N28" s="21" t="inlineStr">
@@ -28807,7 +28807,7 @@
           <t>N | 272呎 (1房)
 $516万
 $18,982/呎
-(26年-04月-26日)</t>
+(26年-04月-27日)</t>
         </is>
       </c>
       <c r="O28" s="21" t="inlineStr">
@@ -28815,7 +28815,7 @@
           <t>P | 268呎 (1房)
 $507万
 $18,914/呎
-(26年-04月-12日)</t>
+(26年-04月-13日)</t>
         </is>
       </c>
       <c r="P28" s="21" t="inlineStr">
@@ -28823,7 +28823,7 @@
           <t>Q | 367呎 (2房)
 $694万
 $18,914/呎
-(25年-12月-05日)</t>
+(25年-12月-06日)</t>
         </is>
       </c>
     </row>
@@ -28838,7 +28838,7 @@
           <t>A | 465呎 (3房)
 $765万
 $16,450/呎
-(25年-10月-07日)</t>
+(25年-10月-08日)</t>
         </is>
       </c>
       <c r="C29" s="21" t="inlineStr">
@@ -28846,7 +28846,7 @@
           <t>B | 349呎 (2房)
 $589万
 $16,883/呎
-(25年-10月-19日)</t>
+(25年-10月-20日)</t>
         </is>
       </c>
       <c r="D29" s="21" t="inlineStr">
@@ -28854,7 +28854,7 @@
           <t>C | 349呎 (2房)
 $623万
 $17,848/呎
-(25年-10月-07日)</t>
+(25年-10月-08日)</t>
         </is>
       </c>
       <c r="E29" s="21" t="inlineStr">
@@ -28862,7 +28862,7 @@
           <t>D | 349呎 (2房)
 $577万
 $16,540/呎
-(25年-10月-09日)</t>
+(25年-10月-10日)</t>
         </is>
       </c>
       <c r="F29" s="21" t="inlineStr">
@@ -28870,7 +28870,7 @@
           <t>E | 350呎 (2房)
 $613万
 $17,518/呎
-(25年-10月-08日)</t>
+(25年-10月-09日)</t>
         </is>
       </c>
       <c r="G29" s="21" t="inlineStr">
@@ -28878,7 +28878,7 @@
           <t>F | 269呎 (1房)
 $492万
 $18,281/呎
-(26年-04月-16日)</t>
+(26年-04月-17日)</t>
         </is>
       </c>
       <c r="H29" s="21" t="inlineStr">
@@ -28886,7 +28886,7 @@
           <t>G | 269呎 (1房)
 $462万
 $17,190/呎
-(25年-10月-15日)</t>
+(25年-10月-16日)</t>
         </is>
       </c>
       <c r="I29" s="21" t="inlineStr">
@@ -28894,7 +28894,7 @@
           <t>H | 379呎 (2房)
 $655万
 $17,283/呎
-(25年-10月-13日)</t>
+(25年-10月-14日)</t>
         </is>
       </c>
       <c r="J29" s="21" t="inlineStr">
@@ -28902,7 +28902,7 @@
           <t>J | 320呎 (2房)
 $591万
 $18,478/呎
-(25年-11月-12日)</t>
+(25年-11月-13日)</t>
         </is>
       </c>
       <c r="K29" s="21" t="inlineStr">
@@ -28910,7 +28910,7 @@
           <t>K | 269呎 (1房)
 $482万
 $17,925/呎
-(26年-03月-29日)</t>
+(26年-03月-30日)</t>
         </is>
       </c>
       <c r="L29" s="21" t="inlineStr">
@@ -28918,7 +28918,7 @@
           <t>L | 272呎 (1房)
 $484万
 $17,795/呎
-(25年-10月-23日)</t>
+(25年-10月-24日)</t>
         </is>
       </c>
       <c r="M29" s="21" t="inlineStr">
@@ -28926,7 +28926,7 @@
           <t>M | 272呎 (1房)
 $522万
 $19,189/呎
-(26年-04月-14日)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="N29" s="21" t="inlineStr">
@@ -28934,7 +28934,7 @@
           <t>N | 272呎 (1房)
 $507万
 $18,628/呎
-(26年-04月-26日)</t>
+(26年-04月-27日)</t>
         </is>
       </c>
       <c r="O29" s="21" t="inlineStr">
@@ -28942,7 +28942,7 @@
           <t>P | 268呎 (1房)
 $505万
 $18,854/呎
-(26年-04月-12日)</t>
+(26年-04月-13日)</t>
         </is>
       </c>
       <c r="P29" s="21" t="inlineStr">
@@ -28950,7 +28950,7 @@
           <t>Q | 367呎 (2房)
 $645万
 $17,570/呎
-(25年-10月-07日)</t>
+(25年-10月-08日)</t>
         </is>
       </c>
     </row>
@@ -28965,7 +28965,7 @@
           <t>A | 465呎 (3房)
 $755万
 $16,233/呎
-(25年-10月-05日)</t>
+(25年-10月-06日)</t>
         </is>
       </c>
       <c r="C30" s="21" t="inlineStr">
@@ -28973,7 +28973,7 @@
           <t>B | 349呎 (2房)
 $613万
 $17,563/呎
-(25年-12月-08日)</t>
+(25年-12月-09日)</t>
         </is>
       </c>
       <c r="D30" s="21" t="inlineStr">
@@ -28981,7 +28981,7 @@
           <t>C | 349呎 (2房)
 $582万
 $16,682/呎
-(25年-12月-18日)</t>
+(25年-12月-19日)</t>
         </is>
       </c>
       <c r="E30" s="21" t="inlineStr">
@@ -28989,7 +28989,7 @@
           <t>D | 349呎 (2房)
 $569万
 $16,298/呎
-(25年-10月-08日)</t>
+(25年-10月-09日)</t>
         </is>
       </c>
       <c r="F30" s="21" t="inlineStr">
@@ -28997,7 +28997,7 @@
           <t>E | 350呎 (2房)
 $573万
 $16,375/呎
-(25年-11月-03日)</t>
+(25年-11月-04日)</t>
         </is>
       </c>
       <c r="G30" s="21" t="inlineStr">
@@ -29005,7 +29005,7 @@
           <t>F | 269呎 (1房)
 $487万
 $18,102/呎
-(26年-04月-09日)</t>
+(26年-04月-10日)</t>
         </is>
       </c>
       <c r="H30" s="21" t="inlineStr">
@@ -29013,7 +29013,7 @@
           <t>G | 269呎 (1房)
 $482万
 $17,905/呎
-(25年-10月-21日)</t>
+(25年-10月-22日)</t>
         </is>
       </c>
       <c r="I30" s="21" t="inlineStr">
@@ -29021,7 +29021,7 @@
           <t>H | 379呎 (2房)
 $693万
 $18,276/呎
-(25年-12月-18日)</t>
+(25年-12月-19日)</t>
         </is>
       </c>
       <c r="J30" s="21" t="inlineStr">
@@ -29029,7 +29029,7 @@
           <t>J | 320呎 (2房)
 $557万
 $17,392/呎
-(25年-12月-29日)</t>
+(25年-12月-30日)</t>
         </is>
       </c>
       <c r="K30" s="21" t="inlineStr">
@@ -29037,7 +29037,7 @@
           <t>K | 269呎 (1房)
 $480万
 $17,848/呎
-(26年-03月-25日)</t>
+(26年-03月-26日)</t>
         </is>
       </c>
       <c r="L30" s="21" t="inlineStr">
@@ -29045,7 +29045,7 @@
           <t>L | 272呎 (1房)
 $482万
 $17,708/呎
-(25年-10月-01日)</t>
+(25年-10月-02日)</t>
         </is>
       </c>
       <c r="M30" s="21" t="inlineStr">
@@ -29053,7 +29053,7 @@
           <t>M | 272呎 (1房)
 $494万
 $18,157/呎
-(26年-04月-16日)</t>
+(26年-04月-17日)</t>
         </is>
       </c>
       <c r="N30" s="21" t="inlineStr">
@@ -29061,7 +29061,7 @@
           <t>N | 272呎 (1房)
 $505万
 $18,573/呎
-(26年-04月-28日)</t>
+(26年-04月-29日)</t>
         </is>
       </c>
       <c r="O30" s="21" t="inlineStr">
@@ -29069,7 +29069,7 @@
           <t>P | 268呎 (1房)
 $499万
 $18,613/呎
-(26年-04月-28日)</t>
+(26年-04月-29日)</t>
         </is>
       </c>
       <c r="P30" s="21" t="inlineStr">
@@ -29077,7 +29077,7 @@
           <t>Q | 367呎 (2房)
 $632万
 $17,208/呎
-(25年-10月-23日)</t>
+(25年-10月-24日)</t>
         </is>
       </c>
     </row>
@@ -29092,7 +29092,7 @@
           <t>A | 428呎 (3房)
 $907万
 $21,200/呎
-(26年-04月-15日)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
       <c r="C31" s="21" t="inlineStr">
@@ -29100,7 +29100,7 @@
           <t>B | 312呎 (2房)
 $657万
 $21,051/呎
-(26年-04月-19日)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
       <c r="D31" s="21" t="inlineStr">
@@ -29108,7 +29108,7 @@
           <t>C | 312呎 (2房)
 $697万
 $22,330/呎
-(26年-04月-19日)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
       <c r="E31" s="21" t="inlineStr">
@@ -29116,7 +29116,7 @@
           <t>D | 312呎 (2房)
 $669万
 $21,436/呎
-(26年-04月-19日)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
       <c r="F31" s="21" t="inlineStr">
@@ -29124,7 +29124,7 @@
           <t>E | 312呎 (2房)
 $676万
 $21,672/呎
-(26年-04月-19日)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
       <c r="G31" s="21" t="inlineStr">
@@ -29132,7 +29132,7 @@
           <t>F | 232呎 (1房)
 $536万
 $23,100/呎
-(26年-05月-10日)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
       <c r="H31" s="21" t="inlineStr">
@@ -29140,7 +29140,7 @@
           <t>G | 231呎 (1房)
 $541万
 $23,400/呎
-(26年-04月-16日)</t>
+(26年-04月-17日)</t>
         </is>
       </c>
       <c r="I31" s="21" t="inlineStr">
@@ -29148,7 +29148,7 @@
           <t>H | 343呎 (2房)
 $909万
 $26,500/呎
-(26年-04月-29日)</t>
+(26年-04月-30日)</t>
         </is>
       </c>
       <c r="J31" s="21" t="inlineStr">
@@ -29156,7 +29156,7 @@
           <t>J | 536呎 (3房)
 $1608万
 $30,000/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
       <c r="K31" s="21" t="inlineStr">
@@ -29164,7 +29164,7 @@
           <t>K | 235呎 (1房)
 $790万
 $33,638/呎
-(26年-04月-15日)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
       <c r="L31" s="21" t="inlineStr">
@@ -29172,7 +29172,7 @@
           <t>L | 235呎 (1房)
 $689万
 $29,300/呎
-(26年-06月-04日)</t>
+(26年-06月-05日)</t>
         </is>
       </c>
       <c r="M31" s="21" t="inlineStr">
@@ -29180,7 +29180,7 @@
           <t>M | 234呎 (1房)
 $716万
 $30,603/呎
-(26年-05月-28日)</t>
+(26年-05月-29日)</t>
         </is>
       </c>
       <c r="N31" s="21" t="inlineStr">
@@ -29188,7 +29188,7 @@
           <t>N | 230呎 (1房)
 $639万
 $27,775/呎
-(26年-05月-04日)</t>
+(26年-05月-05日)</t>
         </is>
       </c>
       <c r="O31" s="21" t="inlineStr">
@@ -29196,7 +29196,7 @@
           <t>P | 328呎 (2房)
 $827万
 $25,200/呎
-(26年-06月-08日)</t>
+(26年-06月-09日)</t>
         </is>
       </c>
       <c r="P31" s="23" t="inlineStr"/>

--- a/files/九龙-马头角-壹沐第1期.xlsx
+++ b/files/九龙-马头角-壹沐第1期.xlsx
@@ -1206,14 +1206,14 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
-        <v>6323400</v>
+        <v>6729100</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>23507</v>
+        <v>25015</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
@@ -1221,10 +1221,10 @@
         </is>
       </c>
       <c r="K10" s="5" t="n">
-        <v>6323400</v>
+        <v>6729100</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>23507</v>
+        <v>25015</v>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
@@ -25841,9 +25841,9 @@
       <c r="F5" s="21" t="inlineStr">
         <is>
           <t>E | 269呎 (1房)
-$632万
-$23,507/呎
-(26年-06月-30日)</t>
+$673万
+$25,015/呎
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="G5" s="21" t="inlineStr">
